--- a/public/templates/Plan_Activity_Upload_Template.xlsx
+++ b/public/templates/Plan_Activity_Upload_Template.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_59158B50F63E464C410C56B5C16D5805319BD648" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EA29E47-3D11-40FD-AC7E-47733FDCEBA0}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivek\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B06962-748E-4090-9B3F-DCD23C12EB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Upload" sheetId="1" r:id="rId1"/>
@@ -14,34 +19,23 @@
     <sheet name="How to load" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="REF_DOMAIN">Teams!$C$2:$C$9</definedName>
-    <definedName name="REF_FUNCTION">Teams!$B$2:$B$9</definedName>
+    <definedName name="REF_DOMAIN">Teams!$C$2:$C$7</definedName>
+    <definedName name="REF_FUNCTION">Teams!$B$2:$B$7</definedName>
     <definedName name="REF_IMPACT">Reference!$E$2:$E$3</definedName>
     <definedName name="REF_LAYER">Reference!$B$2:$B$6</definedName>
     <definedName name="REF_LEVEL">Reference!$G$2:$G$6</definedName>
     <definedName name="REF_NETDOMAIN">Reference!$A$2:$A$3</definedName>
     <definedName name="REF_PLANTYPE">Reference!$C$2:$C$8</definedName>
     <definedName name="REF_SHIFT">Reference!$F$2:$F$6</definedName>
-    <definedName name="REF_SUBDOMAIN">Teams!$D$2:$D$9</definedName>
-    <definedName name="REF_TEAMPATH">Teams!$E$2:$E$9</definedName>
+    <definedName name="REF_SUBDOMAIN">Teams!$D$2:$D$7</definedName>
+    <definedName name="REF_TEAMPATH">Teams!$E$2:$E$7</definedName>
     <definedName name="REF_VENDOR">Reference!$D$2:$D$10</definedName>
-    <definedName name="REF_VERTICAL">Teams!$A$2:$A$9</definedName>
+    <definedName name="REF_VERTICAL">Teams!$A$2:$A$7</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -74,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="314">
   <si>
     <t>KEY</t>
   </si>
@@ -197,12 +191,6 @@
     <t>L3</t>
   </si>
   <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
     <t>Scheduling</t>
   </si>
   <si>
@@ -431,48 +419,6 @@
     <t>MPLS Core</t>
   </si>
   <si>
-    <t>System Engineering &gt; Change Management &gt; IP Access &gt; MPLS Core</t>
-  </si>
-  <si>
-    <t>IP Planning</t>
-  </si>
-  <si>
-    <t>System Engineering &gt; Change Management &gt; IP Access &gt; IP Planning</t>
-  </si>
-  <si>
-    <t>Transport Access</t>
-  </si>
-  <si>
-    <t>System Engineering &gt; Change Management &gt; Transport &gt; Transport Access</t>
-  </si>
-  <si>
-    <t>Transport Core</t>
-  </si>
-  <si>
-    <t>System Engineering &gt; Change Management &gt; Transport &gt; Transport Core</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>Operations &gt; NOC &gt; IP Access &gt; MPLS Access</t>
-  </si>
-  <si>
-    <t>NOC IP</t>
-  </si>
-  <si>
-    <t>Operations &gt; NOC &gt; IP Access &gt; NOC IP</t>
-  </si>
-  <si>
-    <t>Field Ops</t>
-  </si>
-  <si>
-    <t>Field MPLS</t>
-  </si>
-  <si>
-    <t>Operations &gt; Field Ops &gt; IP Access &gt; Field MPLS</t>
-  </si>
-  <si>
     <t>Rows 6 and 7 show the problem: 'MPLS Access' exists under two different Team Functions. A bare sub domain name cannot tell them apart, so column P of the Upload sheet takes the full Team Path from column E instead.</t>
   </si>
   <si>
@@ -585,13 +531,493 @@
   </si>
   <si>
     <t>M / E / N / G / ANY, because the procedure parameter is VARCHAR(10) while the UI label ('N 10:00 PM - 7:00 AM') is 20 characters. The Reference sheet holds the mapping.</t>
+  </si>
+  <si>
+    <t>Technology Solutions</t>
+  </si>
+  <si>
+    <t>CCB</t>
+  </si>
+  <si>
+    <t>Packet</t>
+  </si>
+  <si>
+    <t>Packet ECI</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; Packet &gt; Packet ECI</t>
+  </si>
+  <si>
+    <t>CEN Access</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; IP Access &gt; CEN Access</t>
+  </si>
+  <si>
+    <t>Embedded Support</t>
+  </si>
+  <si>
+    <t>Site Shifting</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Embedded Support &gt; Site Shifting</t>
+  </si>
+  <si>
+    <t>Upgradation - Homes</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Embedded Support &gt; Upgradation - Homes</t>
+  </si>
+  <si>
+    <t>Upgradation - IP MPLS</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Embedded Support &gt; Upgradation - IP MPLS</t>
+  </si>
+  <si>
+    <t>Upgradation - Optics</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Embedded Support &gt; Upgradation - Optics</t>
+  </si>
+  <si>
+    <t>OLT Access</t>
+  </si>
+  <si>
+    <t>IP Core</t>
+  </si>
+  <si>
+    <t>BRAS Core</t>
+  </si>
+  <si>
+    <t>CEN Core</t>
+  </si>
+  <si>
+    <t>Optics</t>
+  </si>
+  <si>
+    <t>Network Expansion</t>
+  </si>
+  <si>
+    <t>NNI</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>OTN/LCD</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; IP Core &gt; BRAS Core</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; IP Core &gt; CEN Core</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; IP Core &gt; MPLS Core</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Optics &gt; Network Expansion</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Optics &gt; NNI</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Optics &gt; OTN/LCD</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Optics &gt; Project</t>
+  </si>
+  <si>
+    <t>Packet Change</t>
+  </si>
+  <si>
+    <t>Packet NI</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Packet &gt; Packet Change</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Packet &gt; Packet NI</t>
+  </si>
+  <si>
+    <t>Service Optimisation</t>
+  </si>
+  <si>
+    <t>B2B/IWAN</t>
+  </si>
+  <si>
+    <t>B2C/Telemedia/Mobility</t>
+  </si>
+  <si>
+    <t>BRAS Transport</t>
+  </si>
+  <si>
+    <t>EPT/NPT</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Service Optimisation &gt; B2B/IWAN</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Service Optimisation &gt; B2C/Telemedia/Mobility</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Service Optimisation &gt; BRAS Transport</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; Service Optimisation &gt; EPT/NPT</t>
+  </si>
+  <si>
+    <t>Packet Ciena</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; IP Access &gt; CEN Access</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; IP Access &gt; MPLS Access</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; IP Access &gt; OLT Access</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; IP Core &gt; BRAS Core</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; IP Core &gt; CEN Core</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; IP Core &gt; MPLS Core</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; Optics &gt; Network Expansion</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; Optics &gt; OTN/LCD</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; Packet &gt; Packet Ciena</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; Service Optimisation &gt; B2B/IWAN</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; Service Optimisation &gt; B2C/Telemedia/Mobility</t>
+  </si>
+  <si>
+    <t>Technology Solutions &gt; CCB &gt; Service Optimisation &gt; EPT/NPT</t>
+  </si>
+  <si>
+    <t>Managed NOC</t>
+  </si>
+  <si>
+    <t>Africa NOC (Chennai, Manesar)</t>
+  </si>
+  <si>
+    <t>AWS NOC (Manesar)</t>
+  </si>
+  <si>
+    <t>EIG NOAF (Chennai, Mumbai)</t>
+  </si>
+  <si>
+    <t>GBI NSS (Chennai)</t>
+  </si>
+  <si>
+    <t>Meta NOC (Chennai)</t>
+  </si>
+  <si>
+    <t>Microsoft NOC (Manesar, Chennai)</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Managed NOC &gt; Managed NOC &gt; Africa NOC (Chennai, Manesar)</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Managed NOC &gt; Managed NOC &gt; AWS NOC (Manesar)</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Managed NOC &gt; Managed NOC &gt; EIG NOAF (Chennai, Mumbai)</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Managed NOC &gt; Managed NOC &gt; GBI NSS (Chennai)</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Managed NOC &gt; Managed NOC &gt; Meta NOC (Chennai)</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Managed NOC &gt; Managed NOC &gt; Microsoft NOC (Manesar, Chennai)</t>
+  </si>
+  <si>
+    <t>ILD</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>ITMC</t>
+  </si>
+  <si>
+    <t>CLS 2 Mumbai</t>
+  </si>
+  <si>
+    <t>CLS Chennai</t>
+  </si>
+  <si>
+    <t>CLS Mumbai</t>
+  </si>
+  <si>
+    <t>ITMC Global POP</t>
+  </si>
+  <si>
+    <t>ITMC NOC</t>
+  </si>
+  <si>
+    <t>ITMC NS&amp;SA</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; ILD &gt; CLS &gt; CLS 2 Mumbai</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; ILD &gt; CLS &gt; CLS Chennai</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; ILD &gt; CLS &gt; CLS Mumbai</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; ILD &gt; ITMC &gt; ITMC Global POP</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; ILD &gt; ITMC &gt; ITMC NOC</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; ILD &gt; ITMC &gt; ITMC NS&amp;SA</t>
+  </si>
+  <si>
+    <t>NaaS</t>
+  </si>
+  <si>
+    <t>NOC AT RFS</t>
+  </si>
+  <si>
+    <t>Service AT</t>
+  </si>
+  <si>
+    <t>Service Delivery</t>
+  </si>
+  <si>
+    <t>IP/Packet</t>
+  </si>
+  <si>
+    <t>Optics/Homes</t>
+  </si>
+  <si>
+    <t>B2B</t>
+  </si>
+  <si>
+    <t>B2C</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>Telemedia</t>
+  </si>
+  <si>
+    <t>CEN</t>
+  </si>
+  <si>
+    <t>ISP</t>
+  </si>
+  <si>
+    <t>MPLS</t>
+  </si>
+  <si>
+    <t>Tx</t>
+  </si>
+  <si>
+    <t>Core</t>
+  </si>
+  <si>
+    <t>Internal</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; NaaS &gt; NaaS &gt; NaaS</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; NOC AT RFS &gt; IP/Packet &gt; IP/Packet</t>
+  </si>
+  <si>
+    <t>ystem Engineering &gt; NOC AT RFS &gt; Optics/Homes &gt; Optics/Homes</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service AT &gt; B2B &gt; IP</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service AT &gt; B2B &gt; Media</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service AT &gt; B2C &gt; Mobility</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service AT &gt; B2C &gt; Telemedia</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service Delivery &gt; B2B &gt; CEN</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service Delivery &gt; B2B &gt; ISP</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service Delivery &gt; B2B &gt; MPLS</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service Delivery &gt; B2B &gt; Tx</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service Delivery &gt; B2C &gt; Core</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service Delivery &gt; B2C &gt; Internal</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service Delivery &gt; B2C &gt; Mobility</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Service Delivery &gt; B2C &gt; Telemedia</t>
+  </si>
+  <si>
+    <t>Service Experience</t>
+  </si>
+  <si>
+    <t>SOC</t>
+  </si>
+  <si>
+    <t>Ciena EPT</t>
+  </si>
+  <si>
+    <t>FTTH Mobility</t>
+  </si>
+  <si>
+    <t>IP SOC</t>
+  </si>
+  <si>
+    <t>Optics SOC</t>
+  </si>
+  <si>
+    <t>Service Monitoring Desk</t>
+  </si>
+  <si>
+    <t>Service Experience &gt; SOC &gt; Mobility &gt; Ciena EPT</t>
+  </si>
+  <si>
+    <t>Service Experience &gt; SOC &gt; Mobility &gt; FTTH Mobility</t>
+  </si>
+  <si>
+    <t>Service Experience &gt; SOC &gt; Mobility &gt; IP SOC</t>
+  </si>
+  <si>
+    <t>Service Experience &gt; SOC &gt; Mobility &gt; Optics SOC</t>
+  </si>
+  <si>
+    <t>Service Experience &gt; SOC &gt; Mobility &gt; Service Monitoring Desk</t>
+  </si>
+  <si>
+    <t>Infra</t>
+  </si>
+  <si>
+    <t>Incident Management</t>
+  </si>
+  <si>
+    <t>Network Surveillance</t>
+  </si>
+  <si>
+    <t>Change Authorization</t>
+  </si>
+  <si>
+    <t>IRU</t>
+  </si>
+  <si>
+    <t>Access/SDH &amp; Packet</t>
+  </si>
+  <si>
+    <t>OTN/Core</t>
+  </si>
+  <si>
+    <t>IP/Optics</t>
+  </si>
+  <si>
+    <t>IRU/RFMS/OPGW</t>
+  </si>
+  <si>
+    <t>ANG</t>
+  </si>
+  <si>
+    <t>Degradation &amp; WAR Room</t>
+  </si>
+  <si>
+    <t>NOM</t>
+  </si>
+  <si>
+    <t>TNG</t>
+  </si>
+  <si>
+    <t>S&amp;D</t>
+  </si>
+  <si>
+    <t>SYNC &amp; DCN</t>
+  </si>
+  <si>
+    <t>Infra &gt; Network Surveillance &gt; S&amp;D &gt; SYNC &amp; DCN</t>
+  </si>
+  <si>
+    <t>Infra &gt; Network Surveillance &gt; Optics &gt; TNG</t>
+  </si>
+  <si>
+    <t>Infra &gt; Incident Management &gt; IP &gt; CEN</t>
+  </si>
+  <si>
+    <t>Infra &gt; Incident Management &gt; IP &gt; MPLS</t>
+  </si>
+  <si>
+    <t>Infra &gt; Incident Management &gt; Optics &gt; Access/SDH &amp; Packet</t>
+  </si>
+  <si>
+    <t>Infra &gt; Incident Management &gt; Optics &gt; OTN/Core</t>
+  </si>
+  <si>
+    <t>Infra &gt; Network Surveillance &gt; Change Authorization &gt; IP/Optics</t>
+  </si>
+  <si>
+    <t>Infra &gt; Network Surveillance &gt; IP &gt; CEN</t>
+  </si>
+  <si>
+    <t>Infra &gt; Network Surveillance &gt; IP &gt; MPLS</t>
+  </si>
+  <si>
+    <t>Infra &gt; Network Surveillance &gt; IRU &gt; IRU/RFMS/OPGW</t>
+  </si>
+  <si>
+    <t>Infra &gt; Network Surveillance &gt; Optics &gt; ANG</t>
+  </si>
+  <si>
+    <t>Infra &gt; Network Surveillance &gt; Optics &gt; Degradation &amp; WAR Room</t>
+  </si>
+  <si>
+    <t>Infra &gt; Network Surveillance &gt; Optics &gt; NOM</t>
+  </si>
+  <si>
+    <t>System Engineering &gt; Change Management &gt; IP Access &gt; OLT Access</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -702,6 +1128,26 @@
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -814,7 +1260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -931,6 +1377,19 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1202,7 +1661,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T152"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1224,37 +1683,37 @@
     <col min="20" max="20" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="19.5" customHeight="1">
+    <row r="1" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="43" t="s">
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
       <c r="T1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="30" customHeight="1">
+    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1316,7 +1775,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>24</v>
       </c>
@@ -1339,7 +1798,7 @@
         <v>30</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>32</v>
@@ -1348,7 +1807,7 @@
         <v>33</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>34</v>
@@ -1365,27 +1824,27 @@
       <c r="P3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
+      <c r="Q3" s="10">
+        <v>11</v>
+      </c>
+      <c r="R3" s="10">
+        <v>11</v>
+      </c>
+      <c r="S3" s="10">
+        <v>11</v>
+      </c>
       <c r="T3" s="11" t="str">
-        <f>IF($A3="","",IF($L3="CRQ Review",IF(COUNTBLANK($B3:$K3)&gt;0,"Fill plan + activity",IF($O3="","Time (Min) missing","OK")),IF($O3="","Time (Min) missing","OK")))</f>
+        <f t="shared" ref="T3:T34" si="0">IF($A3="","",IF($L3="CRQ Review",IF(COUNTBLANK($B3:$K3)&gt;0,"Fill plan + activity",IF($O3="","Time (Min) missing","OK")),IF($O3="","Time (Min) missing","OK")))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>27</v>
-      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
@@ -1408,25 +1867,27 @@
       <c r="P4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
+      <c r="Q4" s="10">
+        <v>11</v>
+      </c>
+      <c r="R4" s="10">
+        <v>11</v>
+      </c>
+      <c r="S4" s="10">
+        <v>11</v>
+      </c>
       <c r="T4" s="11" t="str">
-        <f>IF($A4="","",IF($L4="CRQ Review",IF(COUNTBLANK($B4:$K4)&gt;0,"Fill plan + activity",IF($O4="","Time (Min) missing","OK")),IF($O4="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>41</v>
-      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
@@ -1435,13 +1896,13 @@
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
       <c r="L5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="O5" s="7">
         <v>30</v>
@@ -1449,15 +1910,21 @@
       <c r="P5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
+      <c r="Q5" s="10">
+        <v>11</v>
+      </c>
+      <c r="R5" s="10">
+        <v>11</v>
+      </c>
+      <c r="S5" s="10">
+        <v>11</v>
+      </c>
       <c r="T5" s="11" t="str">
-        <f>IF($A5="","",IF($L5="CRQ Review",IF(COUNTBLANK($B5:$K5)&gt;0,"Fill plan + activity",IF($O5="","Time (Min) missing","OK")),IF($O5="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>24</v>
       </c>
@@ -1472,10 +1939,10 @@
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
       <c r="L6" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>39</v>
@@ -1486,15 +1953,21 @@
       <c r="P6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
+      <c r="Q6" s="10">
+        <v>11</v>
+      </c>
+      <c r="R6" s="10">
+        <v>11</v>
+      </c>
+      <c r="S6" s="10">
+        <v>11</v>
+      </c>
       <c r="T6" s="11" t="str">
-        <f>IF($A6="","",IF($L6="CRQ Review",IF(COUNTBLANK($B6:$K6)&gt;0,"Fill plan + activity",IF($O6="","Time (Min) missing","OK")),IF($O6="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>24</v>
       </c>
@@ -1509,10 +1982,10 @@
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
       <c r="L7" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N7" s="7" t="s">
         <v>36</v>
@@ -1523,15 +1996,21 @@
       <c r="P7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
+      <c r="Q7" s="10">
+        <v>11</v>
+      </c>
+      <c r="R7" s="10">
+        <v>11</v>
+      </c>
+      <c r="S7" s="10">
+        <v>11</v>
+      </c>
       <c r="T7" s="11" t="str">
-        <f>IF($A7="","",IF($L7="CRQ Review",IF(COUNTBLANK($B7:$K7)&gt;0,"Fill plan + activity",IF($O7="","Time (Min) missing","OK")),IF($O7="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>24</v>
       </c>
@@ -1546,13 +2025,13 @@
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
       <c r="L8" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>35</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O8" s="13">
         <v>360</v>
@@ -1560,23 +2039,23 @@
       <c r="P8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="Q8" s="13">
-        <v>5</v>
-      </c>
-      <c r="R8" s="13">
-        <v>30</v>
-      </c>
-      <c r="S8" s="13">
-        <v>360</v>
+      <c r="Q8" s="10">
+        <v>11</v>
+      </c>
+      <c r="R8" s="10">
+        <v>11</v>
+      </c>
+      <c r="S8" s="10">
+        <v>11</v>
       </c>
       <c r="T8" s="17" t="str">
-        <f>IF($A8="","",IF($L8="CRQ Review",IF(COUNTBLANK($B8:$K8)&gt;0,"Fill plan + activity",IF($O8="","Time (Min) missing","OK")),IF($O8="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -1599,13 +2078,13 @@
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
       <c r="T9" s="11" t="str">
-        <f>IF($A9="","",IF($L9="CRQ Review",IF(COUNTBLANK($B9:$K9)&gt;0,"Fill plan + activity",IF($O9="","Time (Min) missing","OK")),IF($O9="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -1628,13 +2107,13 @@
       <c r="R10" s="10"/>
       <c r="S10" s="10"/>
       <c r="T10" s="11" t="str">
-        <f>IF($A10="","",IF($L10="CRQ Review",IF(COUNTBLANK($B10:$K10)&gt;0,"Fill plan + activity",IF($O10="","Time (Min) missing","OK")),IF($O10="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1647,7 +2126,7 @@
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
       <c r="L11" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
@@ -1657,13 +2136,13 @@
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
       <c r="T11" s="11" t="str">
-        <f>IF($A11="","",IF($L11="CRQ Review",IF(COUNTBLANK($B11:$K11)&gt;0,"Fill plan + activity",IF($O11="","Time (Min) missing","OK")),IF($O11="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -1676,7 +2155,7 @@
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
       <c r="L12" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
@@ -1686,13 +2165,13 @@
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
       <c r="T12" s="11" t="str">
-        <f>IF($A12="","",IF($L12="CRQ Review",IF(COUNTBLANK($B12:$K12)&gt;0,"Fill plan + activity",IF($O12="","Time (Min) missing","OK")),IF($O12="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -1705,7 +2184,7 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
       <c r="L13" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
@@ -1715,13 +2194,13 @@
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
       <c r="T13" s="11" t="str">
-        <f>IF($A13="","",IF($L13="CRQ Review",IF(COUNTBLANK($B13:$K13)&gt;0,"Fill plan + activity",IF($O13="","Time (Min) missing","OK")),IF($O13="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -1734,7 +2213,7 @@
       <c r="J14" s="14"/>
       <c r="K14" s="14"/>
       <c r="L14" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M14" s="21"/>
       <c r="N14" s="21"/>
@@ -1744,13 +2223,13 @@
       <c r="R14" s="21"/>
       <c r="S14" s="21"/>
       <c r="T14" s="17" t="str">
-        <f>IF($A14="","",IF($L14="CRQ Review",IF(COUNTBLANK($B14:$K14)&gt;0,"Fill plan + activity",IF($O14="","Time (Min) missing","OK")),IF($O14="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -1773,13 +2252,13 @@
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
       <c r="T15" s="11" t="str">
-        <f>IF($A15="","",IF($L15="CRQ Review",IF(COUNTBLANK($B15:$K15)&gt;0,"Fill plan + activity",IF($O15="","Time (Min) missing","OK")),IF($O15="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -1802,13 +2281,13 @@
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
       <c r="T16" s="11" t="str">
-        <f>IF($A16="","",IF($L16="CRQ Review",IF(COUNTBLANK($B16:$K16)&gt;0,"Fill plan + activity",IF($O16="","Time (Min) missing","OK")),IF($O16="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -1821,7 +2300,7 @@
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
       <c r="L17" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M17" s="24"/>
       <c r="N17" s="24"/>
@@ -1831,13 +2310,13 @@
       <c r="R17" s="10"/>
       <c r="S17" s="10"/>
       <c r="T17" s="11" t="str">
-        <f>IF($A17="","",IF($L17="CRQ Review",IF(COUNTBLANK($B17:$K17)&gt;0,"Fill plan + activity",IF($O17="","Time (Min) missing","OK")),IF($O17="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -1850,7 +2329,7 @@
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
       <c r="L18" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M18" s="24"/>
       <c r="N18" s="24"/>
@@ -1860,13 +2339,13 @@
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
       <c r="T18" s="11" t="str">
-        <f>IF($A18="","",IF($L18="CRQ Review",IF(COUNTBLANK($B18:$K18)&gt;0,"Fill plan + activity",IF($O18="","Time (Min) missing","OK")),IF($O18="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -1879,7 +2358,7 @@
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
       <c r="L19" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M19" s="24"/>
       <c r="N19" s="24"/>
@@ -1889,13 +2368,13 @@
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
       <c r="T19" s="11" t="str">
-        <f>IF($A19="","",IF($L19="CRQ Review",IF(COUNTBLANK($B19:$K19)&gt;0,"Fill plan + activity",IF($O19="","Time (Min) missing","OK")),IF($O19="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -1908,7 +2387,7 @@
       <c r="J20" s="14"/>
       <c r="K20" s="14"/>
       <c r="L20" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M20" s="27"/>
       <c r="N20" s="27"/>
@@ -1918,13 +2397,13 @@
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="17" t="str">
-        <f>IF($A20="","",IF($L20="CRQ Review",IF(COUNTBLANK($B20:$K20)&gt;0,"Fill plan + activity",IF($O20="","Time (Min) missing","OK")),IF($O20="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -1947,13 +2426,13 @@
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
       <c r="T21" s="11" t="str">
-        <f>IF($A21="","",IF($L21="CRQ Review",IF(COUNTBLANK($B21:$K21)&gt;0,"Fill plan + activity",IF($O21="","Time (Min) missing","OK")),IF($O21="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1976,13 +2455,13 @@
       <c r="R22" s="10"/>
       <c r="S22" s="10"/>
       <c r="T22" s="11" t="str">
-        <f>IF($A22="","",IF($L22="CRQ Review",IF(COUNTBLANK($B22:$K22)&gt;0,"Fill plan + activity",IF($O22="","Time (Min) missing","OK")),IF($O22="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -1995,7 +2474,7 @@
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
       <c r="L23" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
@@ -2005,13 +2484,13 @@
       <c r="R23" s="10"/>
       <c r="S23" s="10"/>
       <c r="T23" s="11" t="str">
-        <f>IF($A23="","",IF($L23="CRQ Review",IF(COUNTBLANK($B23:$K23)&gt;0,"Fill plan + activity",IF($O23="","Time (Min) missing","OK")),IF($O23="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -2024,7 +2503,7 @@
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
       <c r="L24" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
@@ -2034,13 +2513,13 @@
       <c r="R24" s="10"/>
       <c r="S24" s="10"/>
       <c r="T24" s="11" t="str">
-        <f>IF($A24="","",IF($L24="CRQ Review",IF(COUNTBLANK($B24:$K24)&gt;0,"Fill plan + activity",IF($O24="","Time (Min) missing","OK")),IF($O24="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -2053,7 +2532,7 @@
       <c r="J25" s="12"/>
       <c r="K25" s="12"/>
       <c r="L25" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
@@ -2063,13 +2542,13 @@
       <c r="R25" s="10"/>
       <c r="S25" s="10"/>
       <c r="T25" s="11" t="str">
-        <f>IF($A25="","",IF($L25="CRQ Review",IF(COUNTBLANK($B25:$K25)&gt;0,"Fill plan + activity",IF($O25="","Time (Min) missing","OK")),IF($O25="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -2082,7 +2561,7 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M26" s="21"/>
       <c r="N26" s="21"/>
@@ -2092,13 +2571,13 @@
       <c r="R26" s="21"/>
       <c r="S26" s="21"/>
       <c r="T26" s="17" t="str">
-        <f>IF($A26="","",IF($L26="CRQ Review",IF(COUNTBLANK($B26:$K26)&gt;0,"Fill plan + activity",IF($O26="","Time (Min) missing","OK")),IF($O26="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -2121,13 +2600,13 @@
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
       <c r="T27" s="11" t="str">
-        <f>IF($A27="","",IF($L27="CRQ Review",IF(COUNTBLANK($B27:$K27)&gt;0,"Fill plan + activity",IF($O27="","Time (Min) missing","OK")),IF($O27="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -2150,13 +2629,13 @@
       <c r="R28" s="10"/>
       <c r="S28" s="10"/>
       <c r="T28" s="11" t="str">
-        <f>IF($A28="","",IF($L28="CRQ Review",IF(COUNTBLANK($B28:$K28)&gt;0,"Fill plan + activity",IF($O28="","Time (Min) missing","OK")),IF($O28="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2169,7 +2648,7 @@
       <c r="J29" s="12"/>
       <c r="K29" s="12"/>
       <c r="L29" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M29" s="24"/>
       <c r="N29" s="24"/>
@@ -2179,13 +2658,13 @@
       <c r="R29" s="10"/>
       <c r="S29" s="10"/>
       <c r="T29" s="11" t="str">
-        <f>IF($A29="","",IF($L29="CRQ Review",IF(COUNTBLANK($B29:$K29)&gt;0,"Fill plan + activity",IF($O29="","Time (Min) missing","OK")),IF($O29="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -2198,7 +2677,7 @@
       <c r="J30" s="12"/>
       <c r="K30" s="12"/>
       <c r="L30" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M30" s="24"/>
       <c r="N30" s="24"/>
@@ -2208,13 +2687,13 @@
       <c r="R30" s="10"/>
       <c r="S30" s="10"/>
       <c r="T30" s="11" t="str">
-        <f>IF($A30="","",IF($L30="CRQ Review",IF(COUNTBLANK($B30:$K30)&gt;0,"Fill plan + activity",IF($O30="","Time (Min) missing","OK")),IF($O30="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -2227,7 +2706,7 @@
       <c r="J31" s="12"/>
       <c r="K31" s="12"/>
       <c r="L31" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M31" s="24"/>
       <c r="N31" s="24"/>
@@ -2237,13 +2716,13 @@
       <c r="R31" s="10"/>
       <c r="S31" s="10"/>
       <c r="T31" s="11" t="str">
-        <f>IF($A31="","",IF($L31="CRQ Review",IF(COUNTBLANK($B31:$K31)&gt;0,"Fill plan + activity",IF($O31="","Time (Min) missing","OK")),IF($O31="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -2256,7 +2735,7 @@
       <c r="J32" s="14"/>
       <c r="K32" s="14"/>
       <c r="L32" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M32" s="27"/>
       <c r="N32" s="27"/>
@@ -2266,13 +2745,13 @@
       <c r="R32" s="27"/>
       <c r="S32" s="27"/>
       <c r="T32" s="17" t="str">
-        <f>IF($A32="","",IF($L32="CRQ Review",IF(COUNTBLANK($B32:$K32)&gt;0,"Fill plan + activity",IF($O32="","Time (Min) missing","OK")),IF($O32="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -2295,13 +2774,13 @@
       <c r="R33" s="10"/>
       <c r="S33" s="10"/>
       <c r="T33" s="11" t="str">
-        <f>IF($A33="","",IF($L33="CRQ Review",IF(COUNTBLANK($B33:$K33)&gt;0,"Fill plan + activity",IF($O33="","Time (Min) missing","OK")),IF($O33="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="0"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -2324,13 +2803,13 @@
       <c r="R34" s="10"/>
       <c r="S34" s="10"/>
       <c r="T34" s="11" t="str">
-        <f>IF($A34="","",IF($L34="CRQ Review",IF(COUNTBLANK($B34:$K34)&gt;0,"Fill plan + activity",IF($O34="","Time (Min) missing","OK")),IF($O34="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20">
+        <f t="shared" si="0"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -2343,7 +2822,7 @@
       <c r="J35" s="12"/>
       <c r="K35" s="12"/>
       <c r="L35" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M35" s="18"/>
       <c r="N35" s="18"/>
@@ -2353,13 +2832,13 @@
       <c r="R35" s="10"/>
       <c r="S35" s="10"/>
       <c r="T35" s="11" t="str">
-        <f>IF($A35="","",IF($L35="CRQ Review",IF(COUNTBLANK($B35:$K35)&gt;0,"Fill plan + activity",IF($O35="","Time (Min) missing","OK")),IF($O35="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
+        <f t="shared" ref="T35:T66" si="1">IF($A35="","",IF($L35="CRQ Review",IF(COUNTBLANK($B35:$K35)&gt;0,"Fill plan + activity",IF($O35="","Time (Min) missing","OK")),IF($O35="","Time (Min) missing","OK")))</f>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -2372,7 +2851,7 @@
       <c r="J36" s="12"/>
       <c r="K36" s="12"/>
       <c r="L36" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
@@ -2382,13 +2861,13 @@
       <c r="R36" s="10"/>
       <c r="S36" s="10"/>
       <c r="T36" s="11" t="str">
-        <f>IF($A36="","",IF($L36="CRQ Review",IF(COUNTBLANK($B36:$K36)&gt;0,"Fill plan + activity",IF($O36="","Time (Min) missing","OK")),IF($O36="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -2401,7 +2880,7 @@
       <c r="J37" s="12"/>
       <c r="K37" s="12"/>
       <c r="L37" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M37" s="18"/>
       <c r="N37" s="18"/>
@@ -2411,13 +2890,13 @@
       <c r="R37" s="10"/>
       <c r="S37" s="10"/>
       <c r="T37" s="11" t="str">
-        <f>IF($A37="","",IF($L37="CRQ Review",IF(COUNTBLANK($B37:$K37)&gt;0,"Fill plan + activity",IF($O37="","Time (Min) missing","OK")),IF($O37="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -2430,7 +2909,7 @@
       <c r="J38" s="14"/>
       <c r="K38" s="14"/>
       <c r="L38" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M38" s="21"/>
       <c r="N38" s="21"/>
@@ -2440,13 +2919,13 @@
       <c r="R38" s="21"/>
       <c r="S38" s="21"/>
       <c r="T38" s="17" t="str">
-        <f>IF($A38="","",IF($L38="CRQ Review",IF(COUNTBLANK($B38:$K38)&gt;0,"Fill plan + activity",IF($O38="","Time (Min) missing","OK")),IF($O38="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -2469,13 +2948,13 @@
       <c r="R39" s="10"/>
       <c r="S39" s="10"/>
       <c r="T39" s="11" t="str">
-        <f>IF($A39="","",IF($L39="CRQ Review",IF(COUNTBLANK($B39:$K39)&gt;0,"Fill plan + activity",IF($O39="","Time (Min) missing","OK")),IF($O39="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="1"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -2498,13 +2977,13 @@
       <c r="R40" s="10"/>
       <c r="S40" s="10"/>
       <c r="T40" s="11" t="str">
-        <f>IF($A40="","",IF($L40="CRQ Review",IF(COUNTBLANK($B40:$K40)&gt;0,"Fill plan + activity",IF($O40="","Time (Min) missing","OK")),IF($O40="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -2517,7 +2996,7 @@
       <c r="J41" s="12"/>
       <c r="K41" s="12"/>
       <c r="L41" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M41" s="24"/>
       <c r="N41" s="24"/>
@@ -2527,13 +3006,13 @@
       <c r="R41" s="10"/>
       <c r="S41" s="10"/>
       <c r="T41" s="11" t="str">
-        <f>IF($A41="","",IF($L41="CRQ Review",IF(COUNTBLANK($B41:$K41)&gt;0,"Fill plan + activity",IF($O41="","Time (Min) missing","OK")),IF($O41="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -2546,7 +3025,7 @@
       <c r="J42" s="12"/>
       <c r="K42" s="12"/>
       <c r="L42" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M42" s="24"/>
       <c r="N42" s="24"/>
@@ -2556,13 +3035,13 @@
       <c r="R42" s="10"/>
       <c r="S42" s="10"/>
       <c r="T42" s="11" t="str">
-        <f>IF($A42="","",IF($L42="CRQ Review",IF(COUNTBLANK($B42:$K42)&gt;0,"Fill plan + activity",IF($O42="","Time (Min) missing","OK")),IF($O42="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -2575,7 +3054,7 @@
       <c r="J43" s="12"/>
       <c r="K43" s="12"/>
       <c r="L43" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M43" s="24"/>
       <c r="N43" s="24"/>
@@ -2585,13 +3064,13 @@
       <c r="R43" s="10"/>
       <c r="S43" s="10"/>
       <c r="T43" s="11" t="str">
-        <f>IF($A43="","",IF($L43="CRQ Review",IF(COUNTBLANK($B43:$K43)&gt;0,"Fill plan + activity",IF($O43="","Time (Min) missing","OK")),IF($O43="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -2604,7 +3083,7 @@
       <c r="J44" s="14"/>
       <c r="K44" s="14"/>
       <c r="L44" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M44" s="27"/>
       <c r="N44" s="27"/>
@@ -2614,13 +3093,13 @@
       <c r="R44" s="27"/>
       <c r="S44" s="27"/>
       <c r="T44" s="17" t="str">
-        <f>IF($A44="","",IF($L44="CRQ Review",IF(COUNTBLANK($B44:$K44)&gt;0,"Fill plan + activity",IF($O44="","Time (Min) missing","OK")),IF($O44="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
@@ -2643,13 +3122,13 @@
       <c r="R45" s="10"/>
       <c r="S45" s="10"/>
       <c r="T45" s="11" t="str">
-        <f>IF($A45="","",IF($L45="CRQ Review",IF(COUNTBLANK($B45:$K45)&gt;0,"Fill plan + activity",IF($O45="","Time (Min) missing","OK")),IF($O45="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="1"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -2672,13 +3151,13 @@
       <c r="R46" s="10"/>
       <c r="S46" s="10"/>
       <c r="T46" s="11" t="str">
-        <f>IF($A46="","",IF($L46="CRQ Review",IF(COUNTBLANK($B46:$K46)&gt;0,"Fill plan + activity",IF($O46="","Time (Min) missing","OK")),IF($O46="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -2691,7 +3170,7 @@
       <c r="J47" s="12"/>
       <c r="K47" s="12"/>
       <c r="L47" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M47" s="18"/>
       <c r="N47" s="18"/>
@@ -2701,13 +3180,13 @@
       <c r="R47" s="10"/>
       <c r="S47" s="10"/>
       <c r="T47" s="11" t="str">
-        <f>IF($A47="","",IF($L47="CRQ Review",IF(COUNTBLANK($B47:$K47)&gt;0,"Fill plan + activity",IF($O47="","Time (Min) missing","OK")),IF($O47="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -2720,7 +3199,7 @@
       <c r="J48" s="12"/>
       <c r="K48" s="12"/>
       <c r="L48" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M48" s="18"/>
       <c r="N48" s="18"/>
@@ -2730,13 +3209,13 @@
       <c r="R48" s="10"/>
       <c r="S48" s="10"/>
       <c r="T48" s="11" t="str">
-        <f>IF($A48="","",IF($L48="CRQ Review",IF(COUNTBLANK($B48:$K48)&gt;0,"Fill plan + activity",IF($O48="","Time (Min) missing","OK")),IF($O48="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -2749,7 +3228,7 @@
       <c r="J49" s="12"/>
       <c r="K49" s="12"/>
       <c r="L49" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M49" s="18"/>
       <c r="N49" s="18"/>
@@ -2759,13 +3238,13 @@
       <c r="R49" s="10"/>
       <c r="S49" s="10"/>
       <c r="T49" s="11" t="str">
-        <f>IF($A49="","",IF($L49="CRQ Review",IF(COUNTBLANK($B49:$K49)&gt;0,"Fill plan + activity",IF($O49="","Time (Min) missing","OK")),IF($O49="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2778,7 +3257,7 @@
       <c r="J50" s="14"/>
       <c r="K50" s="14"/>
       <c r="L50" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M50" s="21"/>
       <c r="N50" s="21"/>
@@ -2788,13 +3267,13 @@
       <c r="R50" s="21"/>
       <c r="S50" s="21"/>
       <c r="T50" s="17" t="str">
-        <f>IF($A50="","",IF($L50="CRQ Review",IF(COUNTBLANK($B50:$K50)&gt;0,"Fill plan + activity",IF($O50="","Time (Min) missing","OK")),IF($O50="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -2817,13 +3296,13 @@
       <c r="R51" s="10"/>
       <c r="S51" s="10"/>
       <c r="T51" s="11" t="str">
-        <f>IF($A51="","",IF($L51="CRQ Review",IF(COUNTBLANK($B51:$K51)&gt;0,"Fill plan + activity",IF($O51="","Time (Min) missing","OK")),IF($O51="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="1"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="52" spans="1:20">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -2846,13 +3325,13 @@
       <c r="R52" s="10"/>
       <c r="S52" s="10"/>
       <c r="T52" s="11" t="str">
-        <f>IF($A52="","",IF($L52="CRQ Review",IF(COUNTBLANK($B52:$K52)&gt;0,"Fill plan + activity",IF($O52="","Time (Min) missing","OK")),IF($O52="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -2865,7 +3344,7 @@
       <c r="J53" s="12"/>
       <c r="K53" s="12"/>
       <c r="L53" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M53" s="24"/>
       <c r="N53" s="24"/>
@@ -2875,13 +3354,13 @@
       <c r="R53" s="10"/>
       <c r="S53" s="10"/>
       <c r="T53" s="11" t="str">
-        <f>IF($A53="","",IF($L53="CRQ Review",IF(COUNTBLANK($B53:$K53)&gt;0,"Fill plan + activity",IF($O53="","Time (Min) missing","OK")),IF($O53="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -2894,7 +3373,7 @@
       <c r="J54" s="12"/>
       <c r="K54" s="12"/>
       <c r="L54" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M54" s="24"/>
       <c r="N54" s="24"/>
@@ -2904,13 +3383,13 @@
       <c r="R54" s="10"/>
       <c r="S54" s="10"/>
       <c r="T54" s="11" t="str">
-        <f>IF($A54="","",IF($L54="CRQ Review",IF(COUNTBLANK($B54:$K54)&gt;0,"Fill plan + activity",IF($O54="","Time (Min) missing","OK")),IF($O54="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -2923,7 +3402,7 @@
       <c r="J55" s="12"/>
       <c r="K55" s="12"/>
       <c r="L55" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M55" s="24"/>
       <c r="N55" s="24"/>
@@ -2933,13 +3412,13 @@
       <c r="R55" s="10"/>
       <c r="S55" s="10"/>
       <c r="T55" s="11" t="str">
-        <f>IF($A55="","",IF($L55="CRQ Review",IF(COUNTBLANK($B55:$K55)&gt;0,"Fill plan + activity",IF($O55="","Time (Min) missing","OK")),IF($O55="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" s="27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2952,7 +3431,7 @@
       <c r="J56" s="14"/>
       <c r="K56" s="14"/>
       <c r="L56" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M56" s="27"/>
       <c r="N56" s="27"/>
@@ -2962,13 +3441,13 @@
       <c r="R56" s="27"/>
       <c r="S56" s="27"/>
       <c r="T56" s="17" t="str">
-        <f>IF($A56="","",IF($L56="CRQ Review",IF(COUNTBLANK($B56:$K56)&gt;0,"Fill plan + activity",IF($O56="","Time (Min) missing","OK")),IF($O56="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
@@ -2991,13 +3470,13 @@
       <c r="R57" s="10"/>
       <c r="S57" s="10"/>
       <c r="T57" s="11" t="str">
-        <f>IF($A57="","",IF($L57="CRQ Review",IF(COUNTBLANK($B57:$K57)&gt;0,"Fill plan + activity",IF($O57="","Time (Min) missing","OK")),IF($O57="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="1"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -3020,13 +3499,13 @@
       <c r="R58" s="10"/>
       <c r="S58" s="10"/>
       <c r="T58" s="11" t="str">
-        <f>IF($A58="","",IF($L58="CRQ Review",IF(COUNTBLANK($B58:$K58)&gt;0,"Fill plan + activity",IF($O58="","Time (Min) missing","OK")),IF($O58="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -3039,7 +3518,7 @@
       <c r="J59" s="12"/>
       <c r="K59" s="12"/>
       <c r="L59" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M59" s="18"/>
       <c r="N59" s="18"/>
@@ -3049,13 +3528,13 @@
       <c r="R59" s="10"/>
       <c r="S59" s="10"/>
       <c r="T59" s="11" t="str">
-        <f>IF($A59="","",IF($L59="CRQ Review",IF(COUNTBLANK($B59:$K59)&gt;0,"Fill plan + activity",IF($O59="","Time (Min) missing","OK")),IF($O59="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -3068,7 +3547,7 @@
       <c r="J60" s="12"/>
       <c r="K60" s="12"/>
       <c r="L60" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M60" s="18"/>
       <c r="N60" s="18"/>
@@ -3078,13 +3557,13 @@
       <c r="R60" s="10"/>
       <c r="S60" s="10"/>
       <c r="T60" s="11" t="str">
-        <f>IF($A60="","",IF($L60="CRQ Review",IF(COUNTBLANK($B60:$K60)&gt;0,"Fill plan + activity",IF($O60="","Time (Min) missing","OK")),IF($O60="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -3097,7 +3576,7 @@
       <c r="J61" s="12"/>
       <c r="K61" s="12"/>
       <c r="L61" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M61" s="18"/>
       <c r="N61" s="18"/>
@@ -3107,13 +3586,13 @@
       <c r="R61" s="10"/>
       <c r="S61" s="10"/>
       <c r="T61" s="11" t="str">
-        <f>IF($A61="","",IF($L61="CRQ Review",IF(COUNTBLANK($B61:$K61)&gt;0,"Fill plan + activity",IF($O61="","Time (Min) missing","OK")),IF($O61="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -3126,7 +3605,7 @@
       <c r="J62" s="14"/>
       <c r="K62" s="14"/>
       <c r="L62" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M62" s="21"/>
       <c r="N62" s="21"/>
@@ -3136,13 +3615,13 @@
       <c r="R62" s="21"/>
       <c r="S62" s="21"/>
       <c r="T62" s="17" t="str">
-        <f>IF($A62="","",IF($L62="CRQ Review",IF(COUNTBLANK($B62:$K62)&gt;0,"Fill plan + activity",IF($O62="","Time (Min) missing","OK")),IF($O62="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -3165,13 +3644,13 @@
       <c r="R63" s="10"/>
       <c r="S63" s="10"/>
       <c r="T63" s="11" t="str">
-        <f>IF($A63="","",IF($L63="CRQ Review",IF(COUNTBLANK($B63:$K63)&gt;0,"Fill plan + activity",IF($O63="","Time (Min) missing","OK")),IF($O63="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="1"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="64" spans="1:20">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" s="24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -3194,13 +3673,13 @@
       <c r="R64" s="10"/>
       <c r="S64" s="10"/>
       <c r="T64" s="11" t="str">
-        <f>IF($A64="","",IF($L64="CRQ Review",IF(COUNTBLANK($B64:$K64)&gt;0,"Fill plan + activity",IF($O64="","Time (Min) missing","OK")),IF($O64="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" s="24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
@@ -3213,7 +3692,7 @@
       <c r="J65" s="12"/>
       <c r="K65" s="12"/>
       <c r="L65" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M65" s="24"/>
       <c r="N65" s="24"/>
@@ -3223,13 +3702,13 @@
       <c r="R65" s="10"/>
       <c r="S65" s="10"/>
       <c r="T65" s="11" t="str">
-        <f>IF($A65="","",IF($L65="CRQ Review",IF(COUNTBLANK($B65:$K65)&gt;0,"Fill plan + activity",IF($O65="","Time (Min) missing","OK")),IF($O65="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" s="24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
@@ -3242,7 +3721,7 @@
       <c r="J66" s="12"/>
       <c r="K66" s="12"/>
       <c r="L66" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M66" s="24"/>
       <c r="N66" s="24"/>
@@ -3252,13 +3731,13 @@
       <c r="R66" s="10"/>
       <c r="S66" s="10"/>
       <c r="T66" s="11" t="str">
-        <f>IF($A66="","",IF($L66="CRQ Review",IF(COUNTBLANK($B66:$K66)&gt;0,"Fill plan + activity",IF($O66="","Time (Min) missing","OK")),IF($O66="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20">
+        <f t="shared" si="1"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" s="24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
@@ -3271,7 +3750,7 @@
       <c r="J67" s="12"/>
       <c r="K67" s="12"/>
       <c r="L67" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M67" s="24"/>
       <c r="N67" s="24"/>
@@ -3281,13 +3760,13 @@
       <c r="R67" s="10"/>
       <c r="S67" s="10"/>
       <c r="T67" s="11" t="str">
-        <f>IF($A67="","",IF($L67="CRQ Review",IF(COUNTBLANK($B67:$K67)&gt;0,"Fill plan + activity",IF($O67="","Time (Min) missing","OK")),IF($O67="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20">
+        <f t="shared" ref="T67:T98" si="2">IF($A67="","",IF($L67="CRQ Review",IF(COUNTBLANK($B67:$K67)&gt;0,"Fill plan + activity",IF($O67="","Time (Min) missing","OK")),IF($O67="","Time (Min) missing","OK")))</f>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" s="27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -3300,7 +3779,7 @@
       <c r="J68" s="14"/>
       <c r="K68" s="14"/>
       <c r="L68" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M68" s="27"/>
       <c r="N68" s="27"/>
@@ -3310,13 +3789,13 @@
       <c r="R68" s="27"/>
       <c r="S68" s="27"/>
       <c r="T68" s="17" t="str">
-        <f>IF($A68="","",IF($L68="CRQ Review",IF(COUNTBLANK($B68:$K68)&gt;0,"Fill plan + activity",IF($O68="","Time (Min) missing","OK")),IF($O68="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
@@ -3339,13 +3818,13 @@
       <c r="R69" s="10"/>
       <c r="S69" s="10"/>
       <c r="T69" s="11" t="str">
-        <f>IF($A69="","",IF($L69="CRQ Review",IF(COUNTBLANK($B69:$K69)&gt;0,"Fill plan + activity",IF($O69="","Time (Min) missing","OK")),IF($O69="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="2"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="70" spans="1:20">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
@@ -3368,13 +3847,13 @@
       <c r="R70" s="10"/>
       <c r="S70" s="10"/>
       <c r="T70" s="11" t="str">
-        <f>IF($A70="","",IF($L70="CRQ Review",IF(COUNTBLANK($B70:$K70)&gt;0,"Fill plan + activity",IF($O70="","Time (Min) missing","OK")),IF($O70="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -3387,7 +3866,7 @@
       <c r="J71" s="12"/>
       <c r="K71" s="12"/>
       <c r="L71" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M71" s="18"/>
       <c r="N71" s="18"/>
@@ -3397,13 +3876,13 @@
       <c r="R71" s="10"/>
       <c r="S71" s="10"/>
       <c r="T71" s="11" t="str">
-        <f>IF($A71="","",IF($L71="CRQ Review",IF(COUNTBLANK($B71:$K71)&gt;0,"Fill plan + activity",IF($O71="","Time (Min) missing","OK")),IF($O71="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
@@ -3416,7 +3895,7 @@
       <c r="J72" s="12"/>
       <c r="K72" s="12"/>
       <c r="L72" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M72" s="18"/>
       <c r="N72" s="18"/>
@@ -3426,13 +3905,13 @@
       <c r="R72" s="10"/>
       <c r="S72" s="10"/>
       <c r="T72" s="11" t="str">
-        <f>IF($A72="","",IF($L72="CRQ Review",IF(COUNTBLANK($B72:$K72)&gt;0,"Fill plan + activity",IF($O72="","Time (Min) missing","OK")),IF($O72="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
@@ -3445,7 +3924,7 @@
       <c r="J73" s="12"/>
       <c r="K73" s="12"/>
       <c r="L73" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M73" s="18"/>
       <c r="N73" s="18"/>
@@ -3455,13 +3934,13 @@
       <c r="R73" s="10"/>
       <c r="S73" s="10"/>
       <c r="T73" s="11" t="str">
-        <f>IF($A73="","",IF($L73="CRQ Review",IF(COUNTBLANK($B73:$K73)&gt;0,"Fill plan + activity",IF($O73="","Time (Min) missing","OK")),IF($O73="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3474,7 +3953,7 @@
       <c r="J74" s="14"/>
       <c r="K74" s="14"/>
       <c r="L74" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M74" s="21"/>
       <c r="N74" s="21"/>
@@ -3484,13 +3963,13 @@
       <c r="R74" s="21"/>
       <c r="S74" s="21"/>
       <c r="T74" s="17" t="str">
-        <f>IF($A74="","",IF($L74="CRQ Review",IF(COUNTBLANK($B74:$K74)&gt;0,"Fill plan + activity",IF($O74="","Time (Min) missing","OK")),IF($O74="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -3513,13 +3992,13 @@
       <c r="R75" s="10"/>
       <c r="S75" s="10"/>
       <c r="T75" s="11" t="str">
-        <f>IF($A75="","",IF($L75="CRQ Review",IF(COUNTBLANK($B75:$K75)&gt;0,"Fill plan + activity",IF($O75="","Time (Min) missing","OK")),IF($O75="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="2"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="76" spans="1:20">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -3542,13 +4021,13 @@
       <c r="R76" s="10"/>
       <c r="S76" s="10"/>
       <c r="T76" s="11" t="str">
-        <f>IF($A76="","",IF($L76="CRQ Review",IF(COUNTBLANK($B76:$K76)&gt;0,"Fill plan + activity",IF($O76="","Time (Min) missing","OK")),IF($O76="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
@@ -3561,7 +4040,7 @@
       <c r="J77" s="12"/>
       <c r="K77" s="12"/>
       <c r="L77" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M77" s="24"/>
       <c r="N77" s="24"/>
@@ -3571,13 +4050,13 @@
       <c r="R77" s="10"/>
       <c r="S77" s="10"/>
       <c r="T77" s="11" t="str">
-        <f>IF($A77="","",IF($L77="CRQ Review",IF(COUNTBLANK($B77:$K77)&gt;0,"Fill plan + activity",IF($O77="","Time (Min) missing","OK")),IF($O77="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
@@ -3590,7 +4069,7 @@
       <c r="J78" s="12"/>
       <c r="K78" s="12"/>
       <c r="L78" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M78" s="24"/>
       <c r="N78" s="24"/>
@@ -3600,13 +4079,13 @@
       <c r="R78" s="10"/>
       <c r="S78" s="10"/>
       <c r="T78" s="11" t="str">
-        <f>IF($A78="","",IF($L78="CRQ Review",IF(COUNTBLANK($B78:$K78)&gt;0,"Fill plan + activity",IF($O78="","Time (Min) missing","OK")),IF($O78="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
@@ -3619,7 +4098,7 @@
       <c r="J79" s="12"/>
       <c r="K79" s="12"/>
       <c r="L79" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M79" s="24"/>
       <c r="N79" s="24"/>
@@ -3629,13 +4108,13 @@
       <c r="R79" s="10"/>
       <c r="S79" s="10"/>
       <c r="T79" s="11" t="str">
-        <f>IF($A79="","",IF($L79="CRQ Review",IF(COUNTBLANK($B79:$K79)&gt;0,"Fill plan + activity",IF($O79="","Time (Min) missing","OK")),IF($O79="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" s="27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -3648,7 +4127,7 @@
       <c r="J80" s="14"/>
       <c r="K80" s="14"/>
       <c r="L80" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M80" s="27"/>
       <c r="N80" s="27"/>
@@ -3658,13 +4137,13 @@
       <c r="R80" s="27"/>
       <c r="S80" s="27"/>
       <c r="T80" s="17" t="str">
-        <f>IF($A80="","",IF($L80="CRQ Review",IF(COUNTBLANK($B80:$K80)&gt;0,"Fill plan + activity",IF($O80="","Time (Min) missing","OK")),IF($O80="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
@@ -3687,13 +4166,13 @@
       <c r="R81" s="10"/>
       <c r="S81" s="10"/>
       <c r="T81" s="11" t="str">
-        <f>IF($A81="","",IF($L81="CRQ Review",IF(COUNTBLANK($B81:$K81)&gt;0,"Fill plan + activity",IF($O81="","Time (Min) missing","OK")),IF($O81="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="2"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="82" spans="1:20">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
@@ -3716,13 +4195,13 @@
       <c r="R82" s="10"/>
       <c r="S82" s="10"/>
       <c r="T82" s="11" t="str">
-        <f>IF($A82="","",IF($L82="CRQ Review",IF(COUNTBLANK($B82:$K82)&gt;0,"Fill plan + activity",IF($O82="","Time (Min) missing","OK")),IF($O82="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
@@ -3735,7 +4214,7 @@
       <c r="J83" s="12"/>
       <c r="K83" s="12"/>
       <c r="L83" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M83" s="18"/>
       <c r="N83" s="18"/>
@@ -3745,13 +4224,13 @@
       <c r="R83" s="10"/>
       <c r="S83" s="10"/>
       <c r="T83" s="11" t="str">
-        <f>IF($A83="","",IF($L83="CRQ Review",IF(COUNTBLANK($B83:$K83)&gt;0,"Fill plan + activity",IF($O83="","Time (Min) missing","OK")),IF($O83="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
@@ -3764,7 +4243,7 @@
       <c r="J84" s="12"/>
       <c r="K84" s="12"/>
       <c r="L84" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M84" s="18"/>
       <c r="N84" s="18"/>
@@ -3774,13 +4253,13 @@
       <c r="R84" s="10"/>
       <c r="S84" s="10"/>
       <c r="T84" s="11" t="str">
-        <f>IF($A84="","",IF($L84="CRQ Review",IF(COUNTBLANK($B84:$K84)&gt;0,"Fill plan + activity",IF($O84="","Time (Min) missing","OK")),IF($O84="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
@@ -3793,7 +4272,7 @@
       <c r="J85" s="12"/>
       <c r="K85" s="12"/>
       <c r="L85" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M85" s="18"/>
       <c r="N85" s="18"/>
@@ -3803,13 +4282,13 @@
       <c r="R85" s="10"/>
       <c r="S85" s="10"/>
       <c r="T85" s="11" t="str">
-        <f>IF($A85="","",IF($L85="CRQ Review",IF(COUNTBLANK($B85:$K85)&gt;0,"Fill plan + activity",IF($O85="","Time (Min) missing","OK")),IF($O85="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" s="21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -3822,7 +4301,7 @@
       <c r="J86" s="14"/>
       <c r="K86" s="14"/>
       <c r="L86" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M86" s="21"/>
       <c r="N86" s="21"/>
@@ -3832,13 +4311,13 @@
       <c r="R86" s="21"/>
       <c r="S86" s="21"/>
       <c r="T86" s="17" t="str">
-        <f>IF($A86="","",IF($L86="CRQ Review",IF(COUNTBLANK($B86:$K86)&gt;0,"Fill plan + activity",IF($O86="","Time (Min) missing","OK")),IF($O86="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -3861,13 +4340,13 @@
       <c r="R87" s="10"/>
       <c r="S87" s="10"/>
       <c r="T87" s="11" t="str">
-        <f>IF($A87="","",IF($L87="CRQ Review",IF(COUNTBLANK($B87:$K87)&gt;0,"Fill plan + activity",IF($O87="","Time (Min) missing","OK")),IF($O87="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="2"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="88" spans="1:20">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
@@ -3890,13 +4369,13 @@
       <c r="R88" s="10"/>
       <c r="S88" s="10"/>
       <c r="T88" s="11" t="str">
-        <f>IF($A88="","",IF($L88="CRQ Review",IF(COUNTBLANK($B88:$K88)&gt;0,"Fill plan + activity",IF($O88="","Time (Min) missing","OK")),IF($O88="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
@@ -3909,7 +4388,7 @@
       <c r="J89" s="12"/>
       <c r="K89" s="12"/>
       <c r="L89" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M89" s="24"/>
       <c r="N89" s="24"/>
@@ -3919,13 +4398,13 @@
       <c r="R89" s="10"/>
       <c r="S89" s="10"/>
       <c r="T89" s="11" t="str">
-        <f>IF($A89="","",IF($L89="CRQ Review",IF(COUNTBLANK($B89:$K89)&gt;0,"Fill plan + activity",IF($O89="","Time (Min) missing","OK")),IF($O89="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
@@ -3938,7 +4417,7 @@
       <c r="J90" s="12"/>
       <c r="K90" s="12"/>
       <c r="L90" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M90" s="24"/>
       <c r="N90" s="24"/>
@@ -3948,13 +4427,13 @@
       <c r="R90" s="10"/>
       <c r="S90" s="10"/>
       <c r="T90" s="11" t="str">
-        <f>IF($A90="","",IF($L90="CRQ Review",IF(COUNTBLANK($B90:$K90)&gt;0,"Fill plan + activity",IF($O90="","Time (Min) missing","OK")),IF($O90="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
@@ -3967,7 +4446,7 @@
       <c r="J91" s="12"/>
       <c r="K91" s="12"/>
       <c r="L91" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M91" s="24"/>
       <c r="N91" s="24"/>
@@ -3977,13 +4456,13 @@
       <c r="R91" s="10"/>
       <c r="S91" s="10"/>
       <c r="T91" s="11" t="str">
-        <f>IF($A91="","",IF($L91="CRQ Review",IF(COUNTBLANK($B91:$K91)&gt;0,"Fill plan + activity",IF($O91="","Time (Min) missing","OK")),IF($O91="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" s="27" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -3996,7 +4475,7 @@
       <c r="J92" s="14"/>
       <c r="K92" s="14"/>
       <c r="L92" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M92" s="27"/>
       <c r="N92" s="27"/>
@@ -4006,13 +4485,13 @@
       <c r="R92" s="27"/>
       <c r="S92" s="27"/>
       <c r="T92" s="17" t="str">
-        <f>IF($A92="","",IF($L92="CRQ Review",IF(COUNTBLANK($B92:$K92)&gt;0,"Fill plan + activity",IF($O92="","Time (Min) missing","OK")),IF($O92="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
@@ -4035,13 +4514,13 @@
       <c r="R93" s="10"/>
       <c r="S93" s="10"/>
       <c r="T93" s="11" t="str">
-        <f>IF($A93="","",IF($L93="CRQ Review",IF(COUNTBLANK($B93:$K93)&gt;0,"Fill plan + activity",IF($O93="","Time (Min) missing","OK")),IF($O93="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="2"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="94" spans="1:20">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
@@ -4064,13 +4543,13 @@
       <c r="R94" s="10"/>
       <c r="S94" s="10"/>
       <c r="T94" s="11" t="str">
-        <f>IF($A94="","",IF($L94="CRQ Review",IF(COUNTBLANK($B94:$K94)&gt;0,"Fill plan + activity",IF($O94="","Time (Min) missing","OK")),IF($O94="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
@@ -4083,7 +4562,7 @@
       <c r="J95" s="12"/>
       <c r="K95" s="12"/>
       <c r="L95" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M95" s="18"/>
       <c r="N95" s="18"/>
@@ -4093,13 +4572,13 @@
       <c r="R95" s="10"/>
       <c r="S95" s="10"/>
       <c r="T95" s="11" t="str">
-        <f>IF($A95="","",IF($L95="CRQ Review",IF(COUNTBLANK($B95:$K95)&gt;0,"Fill plan + activity",IF($O95="","Time (Min) missing","OK")),IF($O95="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
@@ -4112,7 +4591,7 @@
       <c r="J96" s="12"/>
       <c r="K96" s="12"/>
       <c r="L96" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M96" s="18"/>
       <c r="N96" s="18"/>
@@ -4122,13 +4601,13 @@
       <c r="R96" s="10"/>
       <c r="S96" s="10"/>
       <c r="T96" s="11" t="str">
-        <f>IF($A96="","",IF($L96="CRQ Review",IF(COUNTBLANK($B96:$K96)&gt;0,"Fill plan + activity",IF($O96="","Time (Min) missing","OK")),IF($O96="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -4141,7 +4620,7 @@
       <c r="J97" s="12"/>
       <c r="K97" s="12"/>
       <c r="L97" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M97" s="18"/>
       <c r="N97" s="18"/>
@@ -4151,13 +4630,13 @@
       <c r="R97" s="10"/>
       <c r="S97" s="10"/>
       <c r="T97" s="11" t="str">
-        <f>IF($A97="","",IF($L97="CRQ Review",IF(COUNTBLANK($B97:$K97)&gt;0,"Fill plan + activity",IF($O97="","Time (Min) missing","OK")),IF($O97="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -4170,7 +4649,7 @@
       <c r="J98" s="14"/>
       <c r="K98" s="14"/>
       <c r="L98" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M98" s="21"/>
       <c r="N98" s="21"/>
@@ -4180,13 +4659,13 @@
       <c r="R98" s="21"/>
       <c r="S98" s="21"/>
       <c r="T98" s="17" t="str">
-        <f>IF($A98="","",IF($L98="CRQ Review",IF(COUNTBLANK($B98:$K98)&gt;0,"Fill plan + activity",IF($O98="","Time (Min) missing","OK")),IF($O98="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20">
+        <f t="shared" si="2"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B99" s="25"/>
       <c r="C99" s="25"/>
@@ -4209,13 +4688,13 @@
       <c r="R99" s="10"/>
       <c r="S99" s="10"/>
       <c r="T99" s="11" t="str">
-        <f>IF($A99="","",IF($L99="CRQ Review",IF(COUNTBLANK($B99:$K99)&gt;0,"Fill plan + activity",IF($O99="","Time (Min) missing","OK")),IF($O99="","Time (Min) missing","OK")))</f>
+        <f t="shared" ref="T99:T130" si="3">IF($A99="","",IF($L99="CRQ Review",IF(COUNTBLANK($B99:$K99)&gt;0,"Fill plan + activity",IF($O99="","Time (Min) missing","OK")),IF($O99="","Time (Min) missing","OK")))</f>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="100" spans="1:20">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
@@ -4238,13 +4717,13 @@
       <c r="R100" s="10"/>
       <c r="S100" s="10"/>
       <c r="T100" s="11" t="str">
-        <f>IF($A100="","",IF($L100="CRQ Review",IF(COUNTBLANK($B100:$K100)&gt;0,"Fill plan + activity",IF($O100="","Time (Min) missing","OK")),IF($O100="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -4257,7 +4736,7 @@
       <c r="J101" s="12"/>
       <c r="K101" s="12"/>
       <c r="L101" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M101" s="24"/>
       <c r="N101" s="24"/>
@@ -4267,13 +4746,13 @@
       <c r="R101" s="10"/>
       <c r="S101" s="10"/>
       <c r="T101" s="11" t="str">
-        <f>IF($A101="","",IF($L101="CRQ Review",IF(COUNTBLANK($B101:$K101)&gt;0,"Fill plan + activity",IF($O101="","Time (Min) missing","OK")),IF($O101="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -4286,7 +4765,7 @@
       <c r="J102" s="12"/>
       <c r="K102" s="12"/>
       <c r="L102" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M102" s="24"/>
       <c r="N102" s="24"/>
@@ -4296,13 +4775,13 @@
       <c r="R102" s="10"/>
       <c r="S102" s="10"/>
       <c r="T102" s="11" t="str">
-        <f>IF($A102="","",IF($L102="CRQ Review",IF(COUNTBLANK($B102:$K102)&gt;0,"Fill plan + activity",IF($O102="","Time (Min) missing","OK")),IF($O102="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
@@ -4315,7 +4794,7 @@
       <c r="J103" s="12"/>
       <c r="K103" s="12"/>
       <c r="L103" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M103" s="24"/>
       <c r="N103" s="24"/>
@@ -4325,13 +4804,13 @@
       <c r="R103" s="10"/>
       <c r="S103" s="10"/>
       <c r="T103" s="11" t="str">
-        <f>IF($A103="","",IF($L103="CRQ Review",IF(COUNTBLANK($B103:$K103)&gt;0,"Fill plan + activity",IF($O103="","Time (Min) missing","OK")),IF($O103="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" s="27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -4344,7 +4823,7 @@
       <c r="J104" s="14"/>
       <c r="K104" s="14"/>
       <c r="L104" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M104" s="27"/>
       <c r="N104" s="27"/>
@@ -4354,13 +4833,13 @@
       <c r="R104" s="27"/>
       <c r="S104" s="27"/>
       <c r="T104" s="17" t="str">
-        <f>IF($A104="","",IF($L104="CRQ Review",IF(COUNTBLANK($B104:$K104)&gt;0,"Fill plan + activity",IF($O104="","Time (Min) missing","OK")),IF($O104="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="105" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B105" s="19"/>
       <c r="C105" s="19"/>
@@ -4383,13 +4862,13 @@
       <c r="R105" s="10"/>
       <c r="S105" s="10"/>
       <c r="T105" s="11" t="str">
-        <f>IF($A105="","",IF($L105="CRQ Review",IF(COUNTBLANK($B105:$K105)&gt;0,"Fill plan + activity",IF($O105="","Time (Min) missing","OK")),IF($O105="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="3"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="106" spans="1:20">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -4412,13 +4891,13 @@
       <c r="R106" s="10"/>
       <c r="S106" s="10"/>
       <c r="T106" s="11" t="str">
-        <f>IF($A106="","",IF($L106="CRQ Review",IF(COUNTBLANK($B106:$K106)&gt;0,"Fill plan + activity",IF($O106="","Time (Min) missing","OK")),IF($O106="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -4431,7 +4910,7 @@
       <c r="J107" s="12"/>
       <c r="K107" s="12"/>
       <c r="L107" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M107" s="18"/>
       <c r="N107" s="18"/>
@@ -4441,13 +4920,13 @@
       <c r="R107" s="10"/>
       <c r="S107" s="10"/>
       <c r="T107" s="11" t="str">
-        <f>IF($A107="","",IF($L107="CRQ Review",IF(COUNTBLANK($B107:$K107)&gt;0,"Fill plan + activity",IF($O107="","Time (Min) missing","OK")),IF($O107="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="108" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -4460,7 +4939,7 @@
       <c r="J108" s="12"/>
       <c r="K108" s="12"/>
       <c r="L108" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M108" s="18"/>
       <c r="N108" s="18"/>
@@ -4470,13 +4949,13 @@
       <c r="R108" s="10"/>
       <c r="S108" s="10"/>
       <c r="T108" s="11" t="str">
-        <f>IF($A108="","",IF($L108="CRQ Review",IF(COUNTBLANK($B108:$K108)&gt;0,"Fill plan + activity",IF($O108="","Time (Min) missing","OK")),IF($O108="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
@@ -4489,7 +4968,7 @@
       <c r="J109" s="12"/>
       <c r="K109" s="12"/>
       <c r="L109" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M109" s="18"/>
       <c r="N109" s="18"/>
@@ -4499,13 +4978,13 @@
       <c r="R109" s="10"/>
       <c r="S109" s="10"/>
       <c r="T109" s="11" t="str">
-        <f>IF($A109="","",IF($L109="CRQ Review",IF(COUNTBLANK($B109:$K109)&gt;0,"Fill plan + activity",IF($O109="","Time (Min) missing","OK")),IF($O109="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="110" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -4518,7 +4997,7 @@
       <c r="J110" s="14"/>
       <c r="K110" s="14"/>
       <c r="L110" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M110" s="21"/>
       <c r="N110" s="21"/>
@@ -4528,13 +5007,13 @@
       <c r="R110" s="21"/>
       <c r="S110" s="21"/>
       <c r="T110" s="17" t="str">
-        <f>IF($A110="","",IF($L110="CRQ Review",IF(COUNTBLANK($B110:$K110)&gt;0,"Fill plan + activity",IF($O110="","Time (Min) missing","OK")),IF($O110="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="111" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" s="24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B111" s="25"/>
       <c r="C111" s="25"/>
@@ -4557,13 +5036,13 @@
       <c r="R111" s="10"/>
       <c r="S111" s="10"/>
       <c r="T111" s="11" t="str">
-        <f>IF($A111="","",IF($L111="CRQ Review",IF(COUNTBLANK($B111:$K111)&gt;0,"Fill plan + activity",IF($O111="","Time (Min) missing","OK")),IF($O111="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="3"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="112" spans="1:20">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112" s="24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -4586,13 +5065,13 @@
       <c r="R112" s="10"/>
       <c r="S112" s="10"/>
       <c r="T112" s="11" t="str">
-        <f>IF($A112="","",IF($L112="CRQ Review",IF(COUNTBLANK($B112:$K112)&gt;0,"Fill plan + activity",IF($O112="","Time (Min) missing","OK")),IF($O112="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="113" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" s="24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -4605,7 +5084,7 @@
       <c r="J113" s="12"/>
       <c r="K113" s="12"/>
       <c r="L113" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M113" s="24"/>
       <c r="N113" s="24"/>
@@ -4615,13 +5094,13 @@
       <c r="R113" s="10"/>
       <c r="S113" s="10"/>
       <c r="T113" s="11" t="str">
-        <f>IF($A113="","",IF($L113="CRQ Review",IF(COUNTBLANK($B113:$K113)&gt;0,"Fill plan + activity",IF($O113="","Time (Min) missing","OK")),IF($O113="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114" s="24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -4634,7 +5113,7 @@
       <c r="J114" s="12"/>
       <c r="K114" s="12"/>
       <c r="L114" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M114" s="24"/>
       <c r="N114" s="24"/>
@@ -4644,16 +5123,20 @@
       <c r="R114" s="10"/>
       <c r="S114" s="10"/>
       <c r="T114" s="11" t="str">
-        <f>IF($A114="","",IF($L114="CRQ Review",IF(COUNTBLANK($B114:$K114)&gt;0,"Fill plan + activity",IF($O114="","Time (Min) missing","OK")),IF($O114="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B115" s="12"/>
-      <c r="C115" s="12"/>
+        <v>63</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="D115" s="12"/>
       <c r="E115" s="12"/>
       <c r="F115" s="12"/>
@@ -4663,7 +5146,7 @@
       <c r="J115" s="12"/>
       <c r="K115" s="12"/>
       <c r="L115" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M115" s="24"/>
       <c r="N115" s="24"/>
@@ -4673,13 +5156,13 @@
       <c r="R115" s="10"/>
       <c r="S115" s="10"/>
       <c r="T115" s="11" t="str">
-        <f>IF($A115="","",IF($L115="CRQ Review",IF(COUNTBLANK($B115:$K115)&gt;0,"Fill plan + activity",IF($O115="","Time (Min) missing","OK")),IF($O115="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" s="27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -4692,7 +5175,7 @@
       <c r="J116" s="14"/>
       <c r="K116" s="14"/>
       <c r="L116" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M116" s="27"/>
       <c r="N116" s="27"/>
@@ -4702,13 +5185,13 @@
       <c r="R116" s="27"/>
       <c r="S116" s="27"/>
       <c r="T116" s="17" t="str">
-        <f>IF($A116="","",IF($L116="CRQ Review",IF(COUNTBLANK($B116:$K116)&gt;0,"Fill plan + activity",IF($O116="","Time (Min) missing","OK")),IF($O116="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B117" s="19"/>
       <c r="C117" s="19"/>
@@ -4731,13 +5214,13 @@
       <c r="R117" s="10"/>
       <c r="S117" s="10"/>
       <c r="T117" s="11" t="str">
-        <f>IF($A117="","",IF($L117="CRQ Review",IF(COUNTBLANK($B117:$K117)&gt;0,"Fill plan + activity",IF($O117="","Time (Min) missing","OK")),IF($O117="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="3"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="118" spans="1:20">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
@@ -4760,13 +5243,13 @@
       <c r="R118" s="10"/>
       <c r="S118" s="10"/>
       <c r="T118" s="11" t="str">
-        <f>IF($A118="","",IF($L118="CRQ Review",IF(COUNTBLANK($B118:$K118)&gt;0,"Fill plan + activity",IF($O118="","Time (Min) missing","OK")),IF($O118="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -4779,7 +5262,7 @@
       <c r="J119" s="12"/>
       <c r="K119" s="12"/>
       <c r="L119" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M119" s="18"/>
       <c r="N119" s="18"/>
@@ -4789,13 +5272,13 @@
       <c r="R119" s="10"/>
       <c r="S119" s="10"/>
       <c r="T119" s="11" t="str">
-        <f>IF($A119="","",IF($L119="CRQ Review",IF(COUNTBLANK($B119:$K119)&gt;0,"Fill plan + activity",IF($O119="","Time (Min) missing","OK")),IF($O119="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="120" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -4808,7 +5291,7 @@
       <c r="J120" s="12"/>
       <c r="K120" s="12"/>
       <c r="L120" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M120" s="18"/>
       <c r="N120" s="18"/>
@@ -4818,13 +5301,13 @@
       <c r="R120" s="10"/>
       <c r="S120" s="10"/>
       <c r="T120" s="11" t="str">
-        <f>IF($A120="","",IF($L120="CRQ Review",IF(COUNTBLANK($B120:$K120)&gt;0,"Fill plan + activity",IF($O120="","Time (Min) missing","OK")),IF($O120="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="121" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
@@ -4837,7 +5320,7 @@
       <c r="J121" s="12"/>
       <c r="K121" s="12"/>
       <c r="L121" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M121" s="18"/>
       <c r="N121" s="18"/>
@@ -4847,13 +5330,13 @@
       <c r="R121" s="10"/>
       <c r="S121" s="10"/>
       <c r="T121" s="11" t="str">
-        <f>IF($A121="","",IF($L121="CRQ Review",IF(COUNTBLANK($B121:$K121)&gt;0,"Fill plan + activity",IF($O121="","Time (Min) missing","OK")),IF($O121="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="122" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -4866,7 +5349,7 @@
       <c r="J122" s="14"/>
       <c r="K122" s="14"/>
       <c r="L122" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M122" s="21"/>
       <c r="N122" s="21"/>
@@ -4876,13 +5359,13 @@
       <c r="R122" s="21"/>
       <c r="S122" s="21"/>
       <c r="T122" s="17" t="str">
-        <f>IF($A122="","",IF($L122="CRQ Review",IF(COUNTBLANK($B122:$K122)&gt;0,"Fill plan + activity",IF($O122="","Time (Min) missing","OK")),IF($O122="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="123" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123" s="24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B123" s="25"/>
       <c r="C123" s="25"/>
@@ -4905,13 +5388,13 @@
       <c r="R123" s="10"/>
       <c r="S123" s="10"/>
       <c r="T123" s="11" t="str">
-        <f>IF($A123="","",IF($L123="CRQ Review",IF(COUNTBLANK($B123:$K123)&gt;0,"Fill plan + activity",IF($O123="","Time (Min) missing","OK")),IF($O123="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="3"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="124" spans="1:20">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124" s="24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
@@ -4934,13 +5417,13 @@
       <c r="R124" s="10"/>
       <c r="S124" s="10"/>
       <c r="T124" s="11" t="str">
-        <f>IF($A124="","",IF($L124="CRQ Review",IF(COUNTBLANK($B124:$K124)&gt;0,"Fill plan + activity",IF($O124="","Time (Min) missing","OK")),IF($O124="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="125" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125" s="24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
@@ -4953,7 +5436,7 @@
       <c r="J125" s="12"/>
       <c r="K125" s="12"/>
       <c r="L125" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M125" s="24"/>
       <c r="N125" s="24"/>
@@ -4963,13 +5446,13 @@
       <c r="R125" s="10"/>
       <c r="S125" s="10"/>
       <c r="T125" s="11" t="str">
-        <f>IF($A125="","",IF($L125="CRQ Review",IF(COUNTBLANK($B125:$K125)&gt;0,"Fill plan + activity",IF($O125="","Time (Min) missing","OK")),IF($O125="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="126" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126" s="24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -4982,7 +5465,7 @@
       <c r="J126" s="12"/>
       <c r="K126" s="12"/>
       <c r="L126" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M126" s="24"/>
       <c r="N126" s="24"/>
@@ -4992,13 +5475,13 @@
       <c r="R126" s="10"/>
       <c r="S126" s="10"/>
       <c r="T126" s="11" t="str">
-        <f>IF($A126="","",IF($L126="CRQ Review",IF(COUNTBLANK($B126:$K126)&gt;0,"Fill plan + activity",IF($O126="","Time (Min) missing","OK")),IF($O126="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="127" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127" s="24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
@@ -5011,7 +5494,7 @@
       <c r="J127" s="12"/>
       <c r="K127" s="12"/>
       <c r="L127" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M127" s="24"/>
       <c r="N127" s="24"/>
@@ -5021,13 +5504,13 @@
       <c r="R127" s="10"/>
       <c r="S127" s="10"/>
       <c r="T127" s="11" t="str">
-        <f>IF($A127="","",IF($L127="CRQ Review",IF(COUNTBLANK($B127:$K127)&gt;0,"Fill plan + activity",IF($O127="","Time (Min) missing","OK")),IF($O127="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="128" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -5040,7 +5523,7 @@
       <c r="J128" s="14"/>
       <c r="K128" s="14"/>
       <c r="L128" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M128" s="27"/>
       <c r="N128" s="27"/>
@@ -5050,13 +5533,13 @@
       <c r="R128" s="27"/>
       <c r="S128" s="27"/>
       <c r="T128" s="17" t="str">
-        <f>IF($A128="","",IF($L128="CRQ Review",IF(COUNTBLANK($B128:$K128)&gt;0,"Fill plan + activity",IF($O128="","Time (Min) missing","OK")),IF($O128="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="129" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B129" s="19"/>
       <c r="C129" s="19"/>
@@ -5079,13 +5562,13 @@
       <c r="R129" s="10"/>
       <c r="S129" s="10"/>
       <c r="T129" s="11" t="str">
-        <f>IF($A129="","",IF($L129="CRQ Review",IF(COUNTBLANK($B129:$K129)&gt;0,"Fill plan + activity",IF($O129="","Time (Min) missing","OK")),IF($O129="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="3"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="130" spans="1:20">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -5108,13 +5591,13 @@
       <c r="R130" s="10"/>
       <c r="S130" s="10"/>
       <c r="T130" s="11" t="str">
-        <f>IF($A130="","",IF($L130="CRQ Review",IF(COUNTBLANK($B130:$K130)&gt;0,"Fill plan + activity",IF($O130="","Time (Min) missing","OK")),IF($O130="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="131" spans="1:20">
+        <f t="shared" si="3"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
@@ -5127,7 +5610,7 @@
       <c r="J131" s="12"/>
       <c r="K131" s="12"/>
       <c r="L131" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M131" s="18"/>
       <c r="N131" s="18"/>
@@ -5137,13 +5620,13 @@
       <c r="R131" s="10"/>
       <c r="S131" s="10"/>
       <c r="T131" s="11" t="str">
-        <f>IF($A131="","",IF($L131="CRQ Review",IF(COUNTBLANK($B131:$K131)&gt;0,"Fill plan + activity",IF($O131="","Time (Min) missing","OK")),IF($O131="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="132" spans="1:20">
+        <f t="shared" ref="T131:T152" si="4">IF($A131="","",IF($L131="CRQ Review",IF(COUNTBLANK($B131:$K131)&gt;0,"Fill plan + activity",IF($O131="","Time (Min) missing","OK")),IF($O131="","Time (Min) missing","OK")))</f>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
@@ -5156,7 +5639,7 @@
       <c r="J132" s="12"/>
       <c r="K132" s="12"/>
       <c r="L132" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M132" s="18"/>
       <c r="N132" s="18"/>
@@ -5166,13 +5649,13 @@
       <c r="R132" s="10"/>
       <c r="S132" s="10"/>
       <c r="T132" s="11" t="str">
-        <f>IF($A132="","",IF($L132="CRQ Review",IF(COUNTBLANK($B132:$K132)&gt;0,"Fill plan + activity",IF($O132="","Time (Min) missing","OK")),IF($O132="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="133" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
@@ -5185,7 +5668,7 @@
       <c r="J133" s="12"/>
       <c r="K133" s="12"/>
       <c r="L133" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M133" s="18"/>
       <c r="N133" s="18"/>
@@ -5195,13 +5678,13 @@
       <c r="R133" s="10"/>
       <c r="S133" s="10"/>
       <c r="T133" s="11" t="str">
-        <f>IF($A133="","",IF($L133="CRQ Review",IF(COUNTBLANK($B133:$K133)&gt;0,"Fill plan + activity",IF($O133="","Time (Min) missing","OK")),IF($O133="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="134" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -5214,7 +5697,7 @@
       <c r="J134" s="14"/>
       <c r="K134" s="14"/>
       <c r="L134" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M134" s="21"/>
       <c r="N134" s="21"/>
@@ -5224,13 +5707,13 @@
       <c r="R134" s="21"/>
       <c r="S134" s="21"/>
       <c r="T134" s="17" t="str">
-        <f>IF($A134="","",IF($L134="CRQ Review",IF(COUNTBLANK($B134:$K134)&gt;0,"Fill plan + activity",IF($O134="","Time (Min) missing","OK")),IF($O134="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="135" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135" s="24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B135" s="25"/>
       <c r="C135" s="25"/>
@@ -5253,13 +5736,13 @@
       <c r="R135" s="10"/>
       <c r="S135" s="10"/>
       <c r="T135" s="11" t="str">
-        <f>IF($A135="","",IF($L135="CRQ Review",IF(COUNTBLANK($B135:$K135)&gt;0,"Fill plan + activity",IF($O135="","Time (Min) missing","OK")),IF($O135="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="4"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="136" spans="1:20">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136" s="24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -5282,13 +5765,13 @@
       <c r="R136" s="10"/>
       <c r="S136" s="10"/>
       <c r="T136" s="11" t="str">
-        <f>IF($A136="","",IF($L136="CRQ Review",IF(COUNTBLANK($B136:$K136)&gt;0,"Fill plan + activity",IF($O136="","Time (Min) missing","OK")),IF($O136="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137" s="24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
@@ -5301,7 +5784,7 @@
       <c r="J137" s="12"/>
       <c r="K137" s="12"/>
       <c r="L137" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M137" s="24"/>
       <c r="N137" s="24"/>
@@ -5311,13 +5794,13 @@
       <c r="R137" s="10"/>
       <c r="S137" s="10"/>
       <c r="T137" s="11" t="str">
-        <f>IF($A137="","",IF($L137="CRQ Review",IF(COUNTBLANK($B137:$K137)&gt;0,"Fill plan + activity",IF($O137="","Time (Min) missing","OK")),IF($O137="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="138" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138" s="24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>
@@ -5330,7 +5813,7 @@
       <c r="J138" s="12"/>
       <c r="K138" s="12"/>
       <c r="L138" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M138" s="24"/>
       <c r="N138" s="24"/>
@@ -5340,13 +5823,13 @@
       <c r="R138" s="10"/>
       <c r="S138" s="10"/>
       <c r="T138" s="11" t="str">
-        <f>IF($A138="","",IF($L138="CRQ Review",IF(COUNTBLANK($B138:$K138)&gt;0,"Fill plan + activity",IF($O138="","Time (Min) missing","OK")),IF($O138="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="139" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139" s="24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
@@ -5359,7 +5842,7 @@
       <c r="J139" s="12"/>
       <c r="K139" s="12"/>
       <c r="L139" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M139" s="24"/>
       <c r="N139" s="24"/>
@@ -5369,13 +5852,13 @@
       <c r="R139" s="10"/>
       <c r="S139" s="10"/>
       <c r="T139" s="11" t="str">
-        <f>IF($A139="","",IF($L139="CRQ Review",IF(COUNTBLANK($B139:$K139)&gt;0,"Fill plan + activity",IF($O139="","Time (Min) missing","OK")),IF($O139="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="140" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140" s="27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -5388,7 +5871,7 @@
       <c r="J140" s="14"/>
       <c r="K140" s="14"/>
       <c r="L140" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M140" s="27"/>
       <c r="N140" s="27"/>
@@ -5398,13 +5881,13 @@
       <c r="R140" s="27"/>
       <c r="S140" s="27"/>
       <c r="T140" s="17" t="str">
-        <f>IF($A140="","",IF($L140="CRQ Review",IF(COUNTBLANK($B140:$K140)&gt;0,"Fill plan + activity",IF($O140="","Time (Min) missing","OK")),IF($O140="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="141" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B141" s="19"/>
       <c r="C141" s="19"/>
@@ -5427,13 +5910,13 @@
       <c r="R141" s="10"/>
       <c r="S141" s="10"/>
       <c r="T141" s="11" t="str">
-        <f>IF($A141="","",IF($L141="CRQ Review",IF(COUNTBLANK($B141:$K141)&gt;0,"Fill plan + activity",IF($O141="","Time (Min) missing","OK")),IF($O141="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="4"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="142" spans="1:20">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
@@ -5456,13 +5939,13 @@
       <c r="R142" s="10"/>
       <c r="S142" s="10"/>
       <c r="T142" s="11" t="str">
-        <f>IF($A142="","",IF($L142="CRQ Review",IF(COUNTBLANK($B142:$K142)&gt;0,"Fill plan + activity",IF($O142="","Time (Min) missing","OK")),IF($O142="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="143" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
@@ -5475,7 +5958,7 @@
       <c r="J143" s="12"/>
       <c r="K143" s="12"/>
       <c r="L143" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M143" s="18"/>
       <c r="N143" s="18"/>
@@ -5485,13 +5968,13 @@
       <c r="R143" s="10"/>
       <c r="S143" s="10"/>
       <c r="T143" s="11" t="str">
-        <f>IF($A143="","",IF($L143="CRQ Review",IF(COUNTBLANK($B143:$K143)&gt;0,"Fill plan + activity",IF($O143="","Time (Min) missing","OK")),IF($O143="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="144" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A144" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B144" s="12"/>
       <c r="C144" s="12"/>
@@ -5504,7 +5987,7 @@
       <c r="J144" s="12"/>
       <c r="K144" s="12"/>
       <c r="L144" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M144" s="18"/>
       <c r="N144" s="18"/>
@@ -5514,13 +5997,13 @@
       <c r="R144" s="10"/>
       <c r="S144" s="10"/>
       <c r="T144" s="11" t="str">
-        <f>IF($A144="","",IF($L144="CRQ Review",IF(COUNTBLANK($B144:$K144)&gt;0,"Fill plan + activity",IF($O144="","Time (Min) missing","OK")),IF($O144="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="145" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B145" s="12"/>
       <c r="C145" s="12"/>
@@ -5533,7 +6016,7 @@
       <c r="J145" s="12"/>
       <c r="K145" s="12"/>
       <c r="L145" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M145" s="18"/>
       <c r="N145" s="18"/>
@@ -5543,13 +6026,13 @@
       <c r="R145" s="10"/>
       <c r="S145" s="10"/>
       <c r="T145" s="11" t="str">
-        <f>IF($A145="","",IF($L145="CRQ Review",IF(COUNTBLANK($B145:$K145)&gt;0,"Fill plan + activity",IF($O145="","Time (Min) missing","OK")),IF($O145="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="146" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" s="21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -5562,7 +6045,7 @@
       <c r="J146" s="14"/>
       <c r="K146" s="14"/>
       <c r="L146" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M146" s="21"/>
       <c r="N146" s="21"/>
@@ -5572,13 +6055,13 @@
       <c r="R146" s="21"/>
       <c r="S146" s="21"/>
       <c r="T146" s="17" t="str">
-        <f>IF($A146="","",IF($L146="CRQ Review",IF(COUNTBLANK($B146:$K146)&gt;0,"Fill plan + activity",IF($O146="","Time (Min) missing","OK")),IF($O146="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="147" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A147" s="24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B147" s="25"/>
       <c r="C147" s="25"/>
@@ -5601,13 +6084,13 @@
       <c r="R147" s="10"/>
       <c r="S147" s="10"/>
       <c r="T147" s="11" t="str">
-        <f>IF($A147="","",IF($L147="CRQ Review",IF(COUNTBLANK($B147:$K147)&gt;0,"Fill plan + activity",IF($O147="","Time (Min) missing","OK")),IF($O147="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="4"/>
         <v>Fill plan + activity</v>
       </c>
     </row>
-    <row r="148" spans="1:20">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A148" s="24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B148" s="12"/>
       <c r="C148" s="12"/>
@@ -5630,13 +6113,13 @@
       <c r="R148" s="10"/>
       <c r="S148" s="10"/>
       <c r="T148" s="11" t="str">
-        <f>IF($A148="","",IF($L148="CRQ Review",IF(COUNTBLANK($B148:$K148)&gt;0,"Fill plan + activity",IF($O148="","Time (Min) missing","OK")),IF($O148="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="149" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A149" s="24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B149" s="12"/>
       <c r="C149" s="12"/>
@@ -5649,7 +6132,7 @@
       <c r="J149" s="12"/>
       <c r="K149" s="12"/>
       <c r="L149" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M149" s="24"/>
       <c r="N149" s="24"/>
@@ -5659,13 +6142,13 @@
       <c r="R149" s="10"/>
       <c r="S149" s="10"/>
       <c r="T149" s="11" t="str">
-        <f>IF($A149="","",IF($L149="CRQ Review",IF(COUNTBLANK($B149:$K149)&gt;0,"Fill plan + activity",IF($O149="","Time (Min) missing","OK")),IF($O149="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="150" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A150" s="24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
@@ -5678,7 +6161,7 @@
       <c r="J150" s="12"/>
       <c r="K150" s="12"/>
       <c r="L150" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M150" s="24"/>
       <c r="N150" s="24"/>
@@ -5688,13 +6171,13 @@
       <c r="R150" s="10"/>
       <c r="S150" s="10"/>
       <c r="T150" s="11" t="str">
-        <f>IF($A150="","",IF($L150="CRQ Review",IF(COUNTBLANK($B150:$K150)&gt;0,"Fill plan + activity",IF($O150="","Time (Min) missing","OK")),IF($O150="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="151" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A151" s="24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B151" s="12"/>
       <c r="C151" s="12"/>
@@ -5707,7 +6190,7 @@
       <c r="J151" s="12"/>
       <c r="K151" s="12"/>
       <c r="L151" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M151" s="24"/>
       <c r="N151" s="24"/>
@@ -5717,13 +6200,13 @@
       <c r="R151" s="10"/>
       <c r="S151" s="10"/>
       <c r="T151" s="11" t="str">
-        <f>IF($A151="","",IF($L151="CRQ Review",IF(COUNTBLANK($B151:$K151)&gt;0,"Fill plan + activity",IF($O151="","Time (Min) missing","OK")),IF($O151="","Time (Min) missing","OK")))</f>
-        <v>Time (Min) missing</v>
-      </c>
-    </row>
-    <row r="152" spans="1:20">
+        <f t="shared" si="4"/>
+        <v>Time (Min) missing</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" s="27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -5736,7 +6219,7 @@
       <c r="J152" s="14"/>
       <c r="K152" s="14"/>
       <c r="L152" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M152" s="27"/>
       <c r="N152" s="27"/>
@@ -5746,7 +6229,7 @@
       <c r="R152" s="27"/>
       <c r="S152" s="27"/>
       <c r="T152" s="17" t="str">
-        <f>IF($A152="","",IF($L152="CRQ Review",IF(COUNTBLANK($B152:$K152)&gt;0,"Fill plan + activity",IF($O152="","Time (Min) missing","OK")),IF($O152="","Time (Min) missing","OK")))</f>
+        <f t="shared" si="4"/>
         <v>Time (Min) missing</v>
       </c>
     </row>
@@ -5755,23 +6238,7 @@
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="L1:S1"/>
   </mergeCells>
-  <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." sqref="B3:B152" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>REF_VERTICAL</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." sqref="C3:C152" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>REF_FUNCTION</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." sqref="D3:D152" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>REF_DOMAIN</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." sqref="E3:E152" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>REF_SUBDOMAIN</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
+  <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." sqref="F3:F152" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>REF_NETDOMAIN</formula1>
       <formula2>0</formula2>
@@ -5800,25 +6267,57 @@
       <formula1>REF_LEVEL</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Numeric value required" error="Whole number only (minutes or days, 0 or more)." sqref="O3:O147 Q8:S8 Q14:S14 Q20:S20 Q26:S26 Q32:S32 Q38:S38 Q44:S44 Q50:S50 Q56:S56 Q62:S62 Q68:S68 Q74:S74 Q80:S80 Q86:S86 Q92:S92 Q98:S98 Q104:S104 Q110:S110 Q116:S116 Q122:S122 Q128:S128 Q134:S134 Q140:S140 Q146:S146 O148:O152 Q152:S152" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Numeric value required" error="Whole number only (minutes or days, 0 or more)." sqref="Q152:S152 Q14:S14 Q20:S20 Q26:S26 Q32:S32 Q38:S38 Q44:S44 Q50:S50 Q56:S56 Q62:S62 Q68:S68 Q74:S74 Q80:S80 Q86:S86 Q92:S92 Q98:S98 Q104:S104 Q110:S110 Q116:S116 Q122:S122 Q128:S128 Q134:S134 Q140:S140 Q146:S146 O3:O152" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." sqref="P3:P152" xr:uid="{00000000-0002-0000-0000-00000C000000}">
-      <formula1>REF_TEAMPATH</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>Teams!$A$2:$A$79</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3:B152</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>Teams!$B$2:$B$79</xm:f>
+          </x14:formula1>
+          <xm:sqref>C3:C152</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." xr:uid="{00000000-0002-0000-0000-000002000000}">
+          <x14:formula1>
+            <xm:f>Teams!$C$2:$C$79</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3:D152</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." xr:uid="{00000000-0002-0000-0000-000003000000}">
+          <x14:formula1>
+            <xm:f>Teams!$D$2:$D$79</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E152</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Not in master list" error="Pick from the list. Add options on the Reference or Teams sheet." xr:uid="{00000000-0002-0000-0000-00000C000000}">
+          <x14:formula1>
+            <xm:f>Teams!$E$2:$E$79</xm:f>
+          </x14:formula1>
+          <xm:sqref>P3:P152</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="4" width="46" customWidth="1"/>
@@ -5829,42 +6328,42 @@
     <col min="13" max="13" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="D1" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="E1" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="F1" s="30" t="s">
         <v>75</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>77</v>
       </c>
       <c r="G1" s="30" t="s">
         <v>17</v>
       </c>
       <c r="I1" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="M1" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M1" s="30" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>29</v>
       </c>
@@ -5881,16 +6380,16 @@
         <v>33</v>
       </c>
       <c r="F2" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="31" t="s">
         <v>81</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>83</v>
       </c>
       <c r="L2" s="31" t="s">
         <v>34</v>
@@ -5899,33 +6398,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="D3" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="E3" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="F3" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="G3" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="31" t="s">
         <v>88</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="J3" s="31" t="s">
-        <v>90</v>
       </c>
       <c r="L3" s="31" t="s">
         <v>38</v>
@@ -5934,15 +6433,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="31" t="s">
         <v>91</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>93</v>
       </c>
       <c r="F4" s="31" t="s">
         <v>35</v>
@@ -5954,108 +6453,108 @@
         <v>35</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L4" s="31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M4" s="32">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>97</v>
-      </c>
       <c r="F5" s="31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G5" s="31" t="s">
         <v>36</v>
       </c>
       <c r="I5" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="31" t="s">
         <v>43</v>
-      </c>
-      <c r="J5" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="L5" s="31" t="s">
-        <v>45</v>
       </c>
       <c r="M5" s="32">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="F6" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="G6" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="I6" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J6" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>104</v>
-      </c>
       <c r="L6" s="31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M6" s="32">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" s="31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L7" s="31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M7" s="32">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C8" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D9" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="31" t="s">
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D10" s="31" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="D9" s="31" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="33" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="D10" s="31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="33" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -6066,32 +6565,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:E82"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="66" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="5" max="5" width="77.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="D1" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="E1" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>25</v>
       </c>
@@ -6099,33 +6599,33 @@
         <v>26</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>27</v>
+      <c r="C3" s="44" t="s">
+        <v>161</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
         <v>25</v>
       </c>
@@ -6133,16 +6633,16 @@
         <v>26</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="31" t="s">
         <v>25</v>
       </c>
@@ -6150,16 +6650,16 @@
         <v>26</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
         <v>25</v>
       </c>
@@ -6167,74 +6667,1264 @@
         <v>26</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="31" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" s="46" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19" s="46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="35" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="31" t="s">
+      <c r="E23" s="46" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="33" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="36" t="s">
-        <v>133</v>
+      <c r="D24" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="46" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="46" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="46" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="46" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="E31" s="46" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" s="46" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" s="46" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="46" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="D35" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="E35" s="46" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" s="46" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="E37" s="46" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="D38" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="E38" s="46" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="E39" s="46" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="E40" s="46" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="E41" s="46" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="C42" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="E42" s="46" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="E43" s="46" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="E44" s="46" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="C45" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="D45" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="E45" s="46" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="D46" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="E46" s="46" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="C47" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="D47" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="E47" s="46" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="E48" s="46" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="D49" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" s="46" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C50" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="D50" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="E50" s="46" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C51" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="D51" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="E51" s="46" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="D52" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="E52" s="46" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C53" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="D53" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="E53" s="46" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C54" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="D54" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="E54" s="46" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C55" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="E55" s="46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C56" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="D56" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="E56" s="46" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="E57" s="46" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C58" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="D58" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="E58" s="46" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C59" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="D59" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="E59" s="46" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C60" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="D60" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="E60" s="46" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C61" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="E61" s="46" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="B62" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C62" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D62" s="43" t="s">
+        <v>275</v>
+      </c>
+      <c r="E62" s="46" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="B63" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C63" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D63" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="E63" s="46" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="B64" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C64" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D64" s="43" t="s">
+        <v>277</v>
+      </c>
+      <c r="E64" s="46" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="B65" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C65" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D65" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="E65" s="46" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="B66" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="C66" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D66" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="E66" s="46" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B67" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="C67" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="D67" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="E67" s="46" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B68" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="C68" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="D68" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="E68" s="46" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B69" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="C69" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D69" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="E69" s="46" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B70" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="C70" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D70" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="E70" s="46" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B71" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C71" s="43" t="s">
+        <v>288</v>
+      </c>
+      <c r="D71" s="43" t="s">
+        <v>292</v>
+      </c>
+      <c r="E71" s="46" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B72" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C72" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="D72" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="E72" s="46" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B73" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C73" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="D73" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="E73" s="46" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B74" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C74" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="D74" s="43" t="s">
+        <v>293</v>
+      </c>
+      <c r="E74" s="46" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B75" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C75" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D75" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="E75" s="46" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B76" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="C76" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D76" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E76" s="46" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B77" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C77" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D77" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="E77" s="46" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B78" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C78" s="43" t="s">
+        <v>298</v>
+      </c>
+      <c r="D78" s="43" t="s">
+        <v>299</v>
+      </c>
+      <c r="E78" s="46" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B79" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C79" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D79" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="E79" s="46" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="36" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -6246,162 +7936,162 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:C25"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="104" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="17.45">
+    <row r="2" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B2" s="37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="39"/>
+    </row>
+    <row r="6" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="40" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B4" s="38" t="s">
+      <c r="C13" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="39"/>
-    </row>
-    <row r="6" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B6" s="40" t="s">
+    </row>
+    <row r="14" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C14" s="41" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B7" s="40" t="s">
+    <row r="15" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C15" s="39"/>
+    </row>
+    <row r="17" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="40" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" ht="15" customHeight="1">
-      <c r="B8" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="41" t="s">
+    </row>
+    <row r="18" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="40" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="40" t="s">
+      <c r="C18" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="C9" s="41" t="s">
+    </row>
+    <row r="19" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="40" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="10" spans="2:3" ht="51.75" customHeight="1">
-      <c r="B10" s="40" t="s">
+      <c r="C19" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="C10" s="41" t="s">
+    </row>
+    <row r="20" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="40" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="40" t="s">
+      <c r="C20" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="41" t="s">
+    </row>
+    <row r="21" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="38" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="40" t="s">
+      <c r="C21" s="39"/>
+    </row>
+    <row r="23" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C23" s="41" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="15" customHeight="1">
-      <c r="B13" s="40" t="s">
+    <row r="24" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C24" s="41" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="15" customHeight="1">
-      <c r="B14" s="40" t="s">
+    <row r="25" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C25" s="41" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B15" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="39"/>
-    </row>
-    <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B18" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B19" s="40" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B20" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B21" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="C21" s="39"/>
-    </row>
-    <row r="23" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B23" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="15" customHeight="1">
-      <c r="B24" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B25" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>
